--- a/Tests/excel/module07_test_cases.xlsx
+++ b/Tests/excel/module07_test_cases.xlsx
@@ -1374,18 +1374,18 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Đổi tên Category với tên hợp lệ</t>
+          <t>Rename Category with a valid name</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng đổi tên danh mục (Category) khi nhập tên mới hợp lệ.</t>
+          <t>Verify functionality for doi ten category (Category) khi enter ten moi hop le.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập (Training Materials).</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -1395,17 +1395,17 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn danh mục "IT".
-2. Nhấp nút "Đổi tên" (Rename).
-3. Nhập tên mới là "Information Technology".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Nhap select category "IT".
+2. Nhap nut "Rename" (Rename).
+3. Enter ten moi la "Information Technology".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo cập nhật thành công.
-Tên danh mục được thay đổi thành "Information Technology" trên giao diện.
-Các khóa học bên trong danh mục vẫn giữ nguyên.</t>
+          <t>System display notification cap nhat successfully.
+Ten category duoc thay doi thanh "Information Technology" tren interface.
+Cac course ben trong category van giu nguyen.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F02, Rule 5.1</t>
+          <t>Related to M07-F02, Rule 5.1</t>
         </is>
       </c>
     </row>
@@ -1448,18 +1448,18 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Đổi tên Category thất bại do để trống tên</t>
+          <t>Category rename fails due to empty name</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn việc đổi tên danh mục thành rỗng.</t>
+          <t>Verify system bao error va ngan chan viec doi ten category thanh rong.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Đổi tên Category.</t>
+          <t>User is logged in as Staff.
+Currently on Rename Category interface.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1469,14 +1469,14 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Xóa toàn bộ nội dung trong ô nhập tên danh mục.
-2. Nhấp nút "Lưu" (Save).</t>
+          <t>1. Delete toan bo noi dung trong o enter ten category.
+2. Nhap nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập tên danh mục (ví dụ: "Category Name is required.").
-Tên danh mục cũ không bị thay đổi.</t>
+          <t>System display notification error requires enter ten category (e.g.: "Category Name is required.").
+Ten category cu khong bi thay doi.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -1519,18 +1519,18 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ chức năng Lưu trữ và Xóa đối với Category</t>
+          <t>Verify Archive and Delete functions are not supported for Category</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không hiển thị các chức năng Lưu trữ (Archive) và Xóa (Delete) đối với danh mục.</t>
+          <t>Verify system not displayed cac chuc nang Archive (Archive) va Delete (Delete) for category.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1540,13 +1540,13 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn danh mục "English".
-2. Quan sát các nút chức năng và menu ngữ cảnh liên quan đến danh mục.</t>
+          <t>1. Nhap select category "English".
+2. Observe cac nut chuc nang va menu ngu cphoto lien quan den category.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Không hiển thị nút hoặc tùy chọn "Xóa" (Delete) hoặc "Lưu trữ" (Archive) đối với danh mục.</t>
+          <t>Khong display nut hoac tuy select "Delete" (Delete) hoac "Archive" (Archive) for category.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F02, Rule 5.1, Out of Scope (Mục 13)</t>
+          <t>Related to M07-F02, Rule 5.1, Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -1589,18 +1589,18 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Xác minh các Category mặc định tồn tại trong hệ thống</t>
+          <t>Verify default Categories exist in system</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra 5 danh mục mặc định được tạo sẵn khi hệ thống hoạt động.</t>
+          <t>Verify 5 category mac dinh duoc create san khi system hoat dong.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Quan sát danh sách các danh mục hiển thị trên màn hình.</t>
+          <t>1. Observe danh sach cac category display tren man hinh.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị đầy đủ 5 danh mục mặc định: "IT", "English", "PLT", "DA", và "Workshops".</t>
+          <t>System display day du 5 category mac dinh: "IT", "English", "PLT", "DA", va "Workshops".</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Mục 3 (Default Categories)</t>
+          <t>Related to M07-F01, Section 3 (Default Categories)</t>
         </is>
       </c>
     </row>
@@ -1658,18 +1658,18 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Tạo khóa học (Course) mới với thông tin hợp lệ</t>
+          <t>Create new course with valid information</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tạo khóa học mới dưới một danh mục khi nhập đầy đủ thông tin hợp lệ.</t>
+          <t>Verify functionality for create new course duoi mot category khi enter day du thong tin hop le.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1679,16 +1679,16 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn danh mục "IT".
-2. Nhấp nút "Tạo khóa học" (Create Course).
-3. Nhập tên khóa học là "Java Programming".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select category "IT".
+2. Nhap nut "Create course" (Create Course).
+3. Enter ten course la "Java Programming".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tạo thành công.
-Khóa học "Java Programming" hiển thị dưới danh mục "IT".</t>
+          <t>System display notification create successfully.
+Khoa hoc "Java Programming" display duoi category "IT".</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.2</t>
+          <t>Related to M07-F01, Rule 5.2</t>
         </is>
       </c>
     </row>
@@ -1731,18 +1731,18 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Tạo khóa học mới thất bại do để trống tên</t>
+          <t>New course creation fails due to empty name</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo khóa học nếu tên khóa học trống.</t>
+          <t>Verify system bao error va ngan chan create course neu ten course trong.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Tạo khóa học mới.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Course interface.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1752,14 +1752,14 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. Để trống trường Tên khóa học.
-2. Nhấp "Lưu" (Save).</t>
+          <t>1. De trong truong Ten course.
+2. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị lỗi yêu cầu nhập tên khóa học (ví dụ: "Course Name is required.").
-Khóa học mới không được tạo.</t>
+          <t>System display error requires enter ten course (e.g.: "Course Name is required.").
+Khoa hoc moi khong duoc create.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -1802,18 +1802,18 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Chỉnh sửa tên khóa học với thông tin hợp lệ</t>
+          <t>Edit course name with valid information</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng chỉnh sửa tên khóa học thành công.</t>
+          <t>Verify functionality for edit ten course successfully.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập. Khóa học "Java Programming" đã tồn tại.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface. Khoa hoc "Java Programming" da ton tai.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1823,16 +1823,16 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Chỉnh sửa" (Edit).
-3. Thay đổi tên khóa học thành "Advanced Java Programming".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Edit" (Edit).
+3. Thay doi ten course thanh "Advanced Java Programming".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu thành công.
-Tên khóa học cập nhật thành "Advanced Java Programming" trên màn hình.</t>
+          <t>System display notification save successfully.
+Ten course cap nhat thanh "Advanced Java Programming" tren man hinh.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.2</t>
+          <t>Related to M07-F01, Rule 5.2</t>
         </is>
       </c>
     </row>
@@ -1875,18 +1875,18 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Lưu trữ khóa học (Archive Course)</t>
+          <t>Archive course (Archive Course)</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng lưu trữ khóa học.</t>
+          <t>Verify functionality for archive course.</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang ở trạng thái Hoạt động (Active) và có các bài học/bài kiểm tra bên dưới.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang o status Hoat dong (Active) va co cac session/exam ben duoi.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1896,15 +1896,15 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn khóa học "Java Programming".
-2. Nhấp chọn nút "Lưu trữ" (Archive).
-3. Xác nhận lưu trữ nếu hệ thống yêu cầu.</t>
+          <t>1. Nhap select course "Java Programming".
+2. Nhap select nut "Archive" (Archive).
+3. Xac nhan archive neu system requires.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu trữ thành công.
-Khóa học thay đổi trạng thái sang đã lưu trữ (Archived) và bị ẩn đi hoặc hiển thị dưới dạng lưu trữ trên màn hình quản lý.</t>
+          <t>System display notification archive successfully.
+Khoa hoc thay doi status sang da archive (Archived) va bi an di hoac display as archive tren man hinh quan ly.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.2, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.2, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -1947,18 +1947,18 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Khôi phục khóa học đã lưu trữ (Restore Course)</t>
+          <t>Khoi phuc course da archive (Restore Course)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng khôi phục một khóa học đã bị lưu trữ.</t>
+          <t>Verify functionality for khoi phuc mot course da bi archive.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang ở trạng thái Lưu trữ (Archived).</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang o status Archive (Archived).</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1968,15 +1968,15 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Tìm và chọn khóa học "Java Programming" trong danh sách lưu trữ.
-2. Nhấp chọn nút "Khôi phục" (Restore).
-3. Xác nhận khôi phục nếu hệ thống yêu cầu.</t>
+          <t>1. Tim va select course "Java Programming" trong danh sach archive.
+2. Nhap select nut "Khoi phuc" (Restore).
+3. Xac nhan khoi phuc neu system requires.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo khôi phục thành công.
-Khóa học trở lại trạng thái hoạt động bình thường.</t>
+          <t>System display notification khoi phuc successfully.
+Khoa hoc tro lai status hoat dong binh thuong.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.2, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.2, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -2019,18 +2019,18 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ xóa vĩnh viễn khóa học</t>
+          <t>Verify khong ho tro permanently deleted course</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không cho phép xóa vĩnh viễn khóa học khỏi cơ sở dữ liệu.</t>
+          <t>Verify system khong allows permanently deleted course khoi co so du lieu.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -2040,13 +2040,13 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Kiểm tra các nút chức năng và menu hành động liên quan đến khóa học.</t>
+          <t>1. Select course "Java Programming".
+2. Verify cac nut chuc nang va menu hanh dong lien quan den course.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Không có tùy chọn "Xóa vĩnh viễn" hoặc "Delete" cho khóa học, chỉ có tùy chọn "Lưu trữ" (Archive).</t>
+          <t>Khong co tuy select "Delete vinh vien" hoac "Delete" cho course, chi co tuy select "Archive" (Archive).</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.2 (Permanent deletion is not allowed), Out of Scope (Mục 13)</t>
+          <t>Related to Rule 5.2 (Permanent deletion is not allowed), Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -2089,37 +2089,37 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài học (Session) mới với thông tin hợp lệ</t>
+          <t>Create session (Session) moi voi thong tin hop le</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tạo bài học mới dưới một khóa học hoạt động.</t>
+          <t>Verify functionality for create session moi duoi mot course hoat dong.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang hoạt động.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang hoat dong.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"; SessionName="Session 01: OOP Basics"; LessonNumber=1; Description="Giới thiệu về lập trình hướng đối tượng"</t>
+          <t>CourseName="Java Programming"; SessionName="Session 01: OOP Basics"; LessonNumber=1; Description="Gioi thieu ve lap trinh huong doi tuong"</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp nút "Thêm bài học" (Add Session).
-3. Nhập Tên bài học là "Session 01: OOP Basics", số bài học là "1", mô tả là "Giới thiệu về lập trình hướng đối tượng".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select course "Java Programming".
+2. Nhap nut "Add session" (Add Session).
+3. Enter Ten session la "Session 01: OOP Basics", so session la "1", mo ta la "Gioi thieu ve lap trinh huong doi tuong".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tạo thành công.
-Session mới hiển thị dưới khóa học "Java Programming".</t>
+          <t>System display notification create successfully.
+Session moi display duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.4</t>
+          <t>Related to M07-F01, Rule 5.4</t>
         </is>
       </c>
     </row>
@@ -2162,18 +2162,18 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Tạo bài học mới thất bại do để trống tên bài học</t>
+          <t>Create session moi failed due to empty name session</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo bài học nếu tên bài học trống.</t>
+          <t>Verify system bao error va ngan chan create session neu ten session trong.</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Thêm bài học mới.</t>
+          <t>User is logged in as Staff.
+Dang o interface Add session moi.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -2183,15 +2183,15 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. Để trống trường Tên bài học.
-2. Nhập các trường thông tin khác hợp lệ.
-3. Nhấp "Lưu" (Save).</t>
+          <t>1. De trong truong Ten session.
+2. Enter cac truong thong tin khac hop le.
+3. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập Tên bài học (ví dụ: "Session Name is required.").
-Bài học mới không được tạo.</t>
+          <t>System display notification error requires enter Ten session (e.g.: "Session Name is required.").
+Bai hoc moi khong duoc create.</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2234,37 +2234,37 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Chỉnh sửa chi tiết bài học (Edit Session)</t>
+          <t>Edit chi tiet session (Edit Session)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng sửa thông tin bài học thành công.</t>
+          <t>Verify functionality for sua thong tin session successfully.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "Session 01: OOP Basics" đã tồn tại dưới khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Bai hoc "Session 01: OOP Basics" da ton tai duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>SessionOldName="Session 01: OOP Basics"; SessionNewName="Session 01: Advanced OOP Basics"; LessonNumber=2; Description="Mô tả mới"</t>
+          <t>SessionOldName="Session 01: OOP Basics"; SessionNewName="Session 01: Advanced OOP Basics"; LessonNumber=2; Description="Mo ta moi"</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Nhấp chọn "Chỉnh sửa" (Edit).
-3. Sửa Tên bài học thành "Session 01: Advanced OOP Basics", Lesson Number thành "2", Description thành "Mô tả mới".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Nhap select "Edit" (Edit).
+3. Sua Ten session thanh "Session 01: Advanced OOP Basics", Lesson Number thanh "2", Description thanh "Mo ta moi".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu thành công.
-Thông tin bài học hiển thị thay đổi mới tương ứng trên giao diện.</t>
+          <t>System display notification save successfully.
+Thong tin session display thay doi moi tuong ung tren interface.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.4</t>
+          <t>Related to M07-F01, Rule 5.4</t>
         </is>
       </c>
     </row>
@@ -2307,18 +2307,18 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Xóa vĩnh viễn bài học (Delete Session)</t>
+          <t>Delete vinh vien session (Delete Session)</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng xóa vĩnh viễn một bài học và các tài liệu đính kèm bên dưới nó.</t>
+          <t>Verify functionality for permanently deleted mot session va cac tai lieu dinh kem ben duoi no.</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "Session 01: OOP Basics" đang tồn tại và có tài liệu đính kèm.</t>
+          <t>User is logged in as Staff.
+Bai hoc "Session 01: OOP Basics" dang ton tai va co tai lieu dinh kem.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2328,17 +2328,17 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Nhấp chọn nút "Xóa" (Delete).
-3. Hệ thống hiển thị hộp thoại yêu cầu xác nhận xóa vĩnh viễn.
-4. Nhấp "Đồng ý" (Confirm).</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Nhap select nut "Delete" (Delete).
+3. System display hop thoai requires xac nhan permanently deleted.
+4. Nhap "Dong y" (Confirm).</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo xóa thành công.
-Bài học và các tài liệu đính kèm bị xóa vĩnh viễn khỏi hệ thống.
-Hành động không thể hoàn tác.</t>
+          <t>System display notification delete successfully.
+Bai hoc va cac tai lieu dinh kem bi permanently deleted khoi system.
+Hanh dong cannot hoan tac.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F04, Rule 5.4, Error Handling (Mục 9)</t>
+          <t>Related to M07-F04, Rule 5.4, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2381,18 +2381,18 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Hủy bỏ thao tác xóa bài học</t>
+          <t>Huy bo thao tac delete session</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra xem khi hủy xác nhận xóa, bài học vẫn được giữ lại.</t>
+          <t>Verify whether khi huy xac nhan delete, session van duoc giu lai.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "Session 01: OOP Basics" đang tồn tại.</t>
+          <t>User is logged in as Staff.
+Bai hoc "Session 01: OOP Basics" dang ton tai.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -2402,16 +2402,16 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Nhấp chọn nút "Xóa" (Delete).
-3. Hệ thống hiển thị hộp thoại xác nhận.
-4. Nhấp chọn "Hủy" (Cancel).</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Nhap select nut "Delete" (Delete).
+3. System display hop thoai xac nhan.
+4. Nhap select "Huy" (Cancel).</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Hộp thoại xác nhận đóng lại.
-Bài học "Session 01: OOP Basics" vẫn tồn tại trong danh sách và không bị xóa.</t>
+          <t>Hop thoai xac nhan dong lai.
+Bai hoc "Session 01: OOP Basics" van ton tai trong danh sach va khong bi delete.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.4, Error Handling (Mục 9)</t>
+          <t>Related to Rule 5.4, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2454,18 +2454,18 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ lưu trữ bài học</t>
+          <t>Verify khong ho tro archive session</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không cho phép lưu trữ bài học, chỉ có thể xóa vĩnh viễn.</t>
+          <t>Verify system khong allows archive session, chi can permanently deleted.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Bài học.</t>
+          <t>User is logged in as Staff.
+Dang o interface Quan ly Bai hoc.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -2475,13 +2475,13 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Kiểm tra các nút chức năng hành động trên bài học.</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Verify cac nut chuc nang hanh dong tren session.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Không xuất hiện tùy chọn "Lưu trữ" (Archive) đối với bài học. Chỉ hỗ trợ tạo, sửa và xóa vĩnh viễn.</t>
+          <t>Khong xuat hien tuy select "Archive" (Archive) for session. Chi ho tro create, sua va permanently deleted.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.4, Out of Scope (Mục 13)</t>
+          <t>Related to Rule 5.4, Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -2524,18 +2524,18 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài kiểm tra (Exam) mới với thông tin hợp lệ</t>
+          <t>Create exam (Exam) moi voi thong tin hop le</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tạo bài kiểm tra mới dưới một khóa học đang hoạt động.</t>
+          <t>Verify functionality for create exam moi duoi mot course dang hoat dong.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang hoạt động.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang hoat dong.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2545,16 +2545,16 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp nút "Thêm bài kiểm tra" (Add Exam).
-3. Nhập Tên bài kiểm tra là "Midterm Exam".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select course "Java Programming".
+2. Nhap nut "Add exam" (Add Exam).
+3. Enter Ten exam la "Midterm Exam".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tạo thành công.
-Bài kiểm tra "Midterm Exam" hiển thị dưới khóa học "Java Programming".</t>
+          <t>System display notification create successfully.
+Bai kiem tra "Midterm Exam" display duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.5</t>
+          <t>Related to M07-F01, Rule 5.5</t>
         </is>
       </c>
     </row>
@@ -2597,18 +2597,18 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Tạo bài kiểm tra mới thất bại do để trống tên</t>
+          <t>Create exam moi failed due to empty name</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn và báo lỗi nếu tên bài kiểm tra trống.</t>
+          <t>Verify system ngan chan va bao error neu ten exam trong.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Thêm bài kiểm tra mới.</t>
+          <t>User is logged in as Staff.
+Dang o interface Add exam moi.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -2618,14 +2618,14 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. Để trống trường Tên bài kiểm tra.
-2. Nhấp "Lưu" (Save).</t>
+          <t>1. De trong truong Ten exam.
+2. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập Tên bài kiểm tra (ví dụ: "Exam Name is required.").
-Bài kiểm tra không được tạo.</t>
+          <t>System display notification error requires enter Ten exam (e.g.: "Exam Name is required.").
+Bai kiem tra khong duoc create.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2668,18 +2668,18 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Chỉnh sửa chi tiết bài kiểm tra (Edit Exam)</t>
+          <t>Edit chi tiet exam (Edit Exam)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng thay đổi tên bài kiểm tra thành công.</t>
+          <t>Verify functionality for thay doi ten exam successfully.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài kiểm tra "Midterm Exam" đã tồn tại dưới khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Bai kiem tra "Midterm Exam" da ton tai duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -2689,16 +2689,16 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Nhấp chọn "Chỉnh sửa" (Edit).
-3. Thay đổi tên thành "Midterm Practical Exam".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select exam "Midterm Exam".
+2. Nhap select "Edit" (Edit).
+3. Thay doi ten thanh "Midterm Practical Exam".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu thành công.
-Tên bài kiểm tra được cập nhật thành "Midterm Practical Exam" trên giao diện.</t>
+          <t>System display notification save successfully.
+Ten exam duoc cap nhat thanh "Midterm Practical Exam" tren interface.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.5</t>
+          <t>Related to M07-F01, Rule 5.5</t>
         </is>
       </c>
     </row>
@@ -2741,18 +2741,18 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Xóa vĩnh viễn bài kiểm tra (Delete Exam)</t>
+          <t>Delete vinh vien exam (Delete Exam)</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng xóa vĩnh viễn một bài kiểm tra và các tài liệu đính kèm bên dưới nó.</t>
+          <t>Verify functionality for permanently deleted mot exam va cac tai lieu dinh kem ben duoi no.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài kiểm tra "Midterm Exam" đang tồn tại và có tài liệu đính kèm.</t>
+          <t>User is logged in as Staff.
+Bai kiem tra "Midterm Exam" dang ton tai va co tai lieu dinh kem.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -2762,16 +2762,16 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Nhấp nút "Xóa" (Delete).
-3. Xác nhận trên hộp thoại hiển thị bằng cách chọn "Đồng ý" (Confirm).</t>
+          <t>1. Select exam "Midterm Exam".
+2. Nhap nut "Delete" (Delete).
+3. Xac nhan tren hop thoai display bang cach select "Dong y" (Confirm).</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo xóa thành công.
-Bài kiểm tra và các tài liệu đính kèm bị xóa vĩnh viễn khỏi hệ thống.
-Hành động không thể hoàn tác.</t>
+          <t>System display notification delete successfully.
+Bai kiem tra va cac tai lieu dinh kem bi permanently deleted khoi system.
+Hanh dong cannot hoan tac.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F05, Rule 5.5, Error Handling (Mục 9)</t>
+          <t>Related to M07-F05, Rule 5.5, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2814,18 +2814,18 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Hủy bỏ thao tác xóa bài kiểm tra</t>
+          <t>Huy bo thao tac delete exam</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra xem bài kiểm tra không bị xóa khi hủy xác nhận.</t>
+          <t>Verify whether exam khong bi delete khi huy xac nhan.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài kiểm tra "Midterm Exam" đang tồn tại.</t>
+          <t>User is logged in as Staff.
+Bai kiem tra "Midterm Exam" dang ton tai.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2835,15 +2835,15 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Nhấp nút "Xóa" (Delete).
-3. Trên hộp thoại xác nhận, chọn "Hủy" (Cancel).</t>
+          <t>1. Select exam "Midterm Exam".
+2. Nhap nut "Delete" (Delete).
+3. Tren hop thoai xac nhan, select "Huy" (Cancel).</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Hộp thoại đóng lại.
-Bài kiểm tra "Midterm Exam" vẫn tồn tại bình thường.</t>
+          <t>Hop thoai dong lai.
+Bai kiem tra "Midterm Exam" van ton tai binh thuong.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2859,11 +2859,11 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.5, Error Handling (Mục 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t>Related to Rule 5.5, Error Handling (Section 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t>TC-M07-022</t>
@@ -2886,18 +2886,18 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ lưu trữ bài kiểm tra</t>
+          <t>Verify khong ho tro archive exam</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không cho phép lưu trữ bài kiểm tra, chỉ có thể xóa vĩnh viễn.</t>
+          <t>Verify system khong allows archive exam, chi can permanently deleted.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Bài kiểm tra.</t>
+          <t>User is logged in as Staff.
+Dang o interface Quan ly Bai kiem tra.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -2907,13 +2907,13 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Kiểm tra các nút hành động trên bài kiểm tra.</t>
+          <t>1. Select exam "Midterm Exam".
+2. Verify cac nut hanh dong tren exam.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Không xuất hiện tùy chọn "Lưu trữ" (Archive) đối với bài kiểm tra.</t>
+          <t>Khong xuat hien tuy select "Archive" (Archive) for exam.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.5, Out of Scope (Mục 13)</t>
+          <t>Related to Rule 5.5, Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -2956,18 +2956,18 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Đính kèm một tài liệu hợp lệ vào Session/Exam</t>
+          <t>Dinh kem mot tai lieu hop le vao Session/Exam</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng đính kèm tài liệu thành công khi nhập đủ nhãn và link Google Drive đúng định dạng.</t>
+          <t>Verify functionality for dinh kem tai lieu successfully khi enter du nhan va link Google Drive dung format.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang tạo hoặc sửa một Session hoặc Exam.</t>
+          <t>User is logged in as Staff.
+Dang create hoac sua mot Session hoac Exam.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2977,15 +2977,15 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>1. Ở phần đính kèm tài liệu (Material Attachments), nhập Nhãn (Label) là "Slides".
-2. Nhập URL là "https://drive.google.com/file/d/1A2B3C4D5E/view".
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. O phan dinh kem tai lieu (Material Attachments), enter Nhan (Label) la "Slides".
+2. Enter URL la "https://drive.google.com/file/d/1A2B3C4D5E/view".
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Tài liệu được lưu thành công.
-Thông tin đính kèm hiển thị chính xác dưới Session/Exam.</t>
+          <t>Tai lieu duoc save successfully.
+Thong tin dinh kem display chinh xac duoi Session/Exam.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Mục 6 (Material Attachments)</t>
+          <t>Related to M07-F06, Section 6 (Material Attachments)</t>
         </is>
       </c>
     </row>
@@ -3028,18 +3028,18 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Đính kèm nhiều tài liệu hợp lệ vào Session/Exam</t>
+          <t>Dinh kem nhieu tai lieu hop le vao Session/Exam</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra việc đính kèm đồng thời nhiều tài liệu hợp lệ vào cùng một bài học hoặc bài kiểm tra.</t>
+          <t>Verify viec dinh kem dong thoi nhieu tai lieu hop le vao cung mot session hoac exam.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang tạo hoặc sửa một Session hoặc Exam.</t>
+          <t>User is logged in as Staff.
+Dang create hoac sua mot Session hoac Exam.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -3049,15 +3049,15 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>1. Ở dòng tài liệu thứ nhất, nhập Nhãn "Slides" and URL "https://drive.google.com/file/d/111/view".
-2. Nhấp thêm dòng mới.
-3. Ở dòng tài liệu thứ hai, nhập Nhãn "Homework" and URL "https://drive.google.com/file/d/222/view".
-4. Nhấn "Lưu" (Save).</t>
+          <t>1. O dong tai lieu thu nhat, enter Nhan "Slides" and URL "https://drive.google.com/file/d/111/view".
+2. Nhap add dong moi.
+3. O dong tai lieu Monday, enter Nhan "Homework" and URL "https://drive.google.com/file/d/222/view".
+4. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>Cả hai tài liệu đính kèm đều được lưu thành công và hiển thị đầy đủ trên giao diện.</t>
+          <t>Ca hai tai lieu dinh kem deu duoc save successfully va display day du tren interface.</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Mục 6</t>
+          <t>Related to M07-F06, Section 6</t>
         </is>
       </c>
     </row>
@@ -3100,18 +3100,18 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Đính kèm tài liệu với dòng hoàn toàn trống (bỏ qua dòng)</t>
+          <t>Dinh kem tai lieu voi dong hoan toan trong (bo qua dong)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống tự động bỏ qua và không báo lỗi khi có dòng tài liệu trống (cả Label và URL đều rỗng).</t>
+          <t>Verify whether system tu dong bo qua va khong bao error khi co dong tai lieu trong (ca Label va URL deu rong).</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -3121,15 +3121,15 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>1. Thêm một dòng đính kèm tài liệu mới.
-2. Để trống cả hai trường Nhãn (Label) và URL.
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. Add mot dong dinh kem tai lieu moi.
+2. De trong ca hai truong Nhan (Label) va URL.
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống lưu trữ thành công các thông tin khác.
-Dòng trống tự động bị bỏ qua (skipped) mà không hiển thị bất kỳ thông báo lỗi nào.</t>
+          <t>System archive successfully cac thong tin khac.
+Dong trong tu dong bi bo qua (skipped) ma not displayed bat ky notification error nao.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Rule 6 (Empty Attachment Rows), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Rule 6 (Empty Attachment Rows), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3172,36 +3172,36 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Đính kèm thất bại do có Nhãn (Label) nhưng để trống URL</t>
+          <t>Dinh kem failed do co Nhan (Label) nhung blank URL</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn lưu và báo lỗi khi nhập nhãn tài liệu nhưng không có link.</t>
+          <t>Verify system ngan chan save va bao error khi enter nhan tai lieu nhung khong co link.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Label="Sách tham khảo"; URL=""</t>
+          <t>Label="Sach tham khao"; URL=""</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>1. Nhập Nhãn (Label) là "Sách tham khảo".
-2. Để trống trường URL.
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. Enter Nhan (Label) la "Sach tham khao".
+2. De trong truong URL.
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập URL cho tài liệu (ví dụ: "URL is required when Label is provided.").
-Tài liệu không được lưu.</t>
+          <t>System bao error requires enter URL cho tai lieu (e.g.: "URL is required when Label is provided.").
+Tai lieu khong duoc save.</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3244,18 +3244,18 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Đính kèm thất bại do có URL nhưng để trống Nhãn (Label)</t>
+          <t>Dinh kem failed do co URL nhung blank Nhan (Label)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn lưu và báo lỗi khi nhập link tài liệu nhưng để trống nhãn.</t>
+          <t>Verify system ngan chan save va bao error khi enter link tai lieu nhung blank nhan.</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -3265,15 +3265,15 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>1. Để trống trường Nhãn (Label).
-2. Nhập URL là "https://drive.google.com/file/d/1A2B3/view".
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. De trong truong Nhan (Label).
+2. Enter URL la "https://drive.google.com/file/d/1A2B3/view".
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Nhãn cho tài liệu (ví dụ: "Label is required when URL is provided.").
-Tài liệu không được lưu.</t>
+          <t>System bao error requires enter Nhan cho tai lieu (e.g.: "Label is required when URL is provided.").
+Tai lieu khong duoc save.</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3316,36 +3316,36 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Đính kèm thất bại do link không phải Google Drive</t>
+          <t>Dinh kem failed do link not Google Drive</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn lưu và báo lỗi định dạng khi nhập link từ dịch vụ lưu trữ khác.</t>
+          <t>Verify system ngan chan save va bao error format khi enter link tu dich vu archive khac.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>Label="Tài liệu"; URL="https://dropbox.com/s/abcdef"</t>
+          <t>Label="Tai lieu"; URL="https://dropbox.com/s/abcdef"</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>1. Nhập Nhãn "Tài liệu".
-2. Nhập URL là "https://dropbox.com/s/abcdef".
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. Enter Nhan "Tai lieu".
+2. Enter URL la "https://dropbox.com/s/abcdef".
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị lỗi kiểm tra định dạng URL (ví dụ: "Must start with https://drive.google.com/").
-Tài liệu không được lưu.</t>
+          <t>System display error kiem tra format URL (e.g.: "Must start with https://drive.google.com/").
+Tai lieu khong duoc save.</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3388,18 +3388,18 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Xuất danh sách Session ra file CSV (Export CSV)</t>
+          <t>Xuat danh sach Session ra file CSV (Export CSV)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tải file CSV chứa thông tin các bài học của khóa học hiện tại.</t>
+          <t>Verify functionality for tai file CSV chua thong tin cac session cua course hien tai.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách Session của khóa học "Java Programming" chứa các bài học và tài liệu.</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach Session cua course "Java Programming" chua cac session va tai lieu.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -3409,15 +3409,15 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>1. Nhấp nút "Xuất CSV" (Export CSV).</t>
+          <t>1. Nhap nut "Xuat CSV" (Export CSV).</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống tải về một file CSV thành công.
-File CSV có các cột: Session ID, Session Name, Lesson Number, Description.
-Thông tin các bài học khớp với danh sách hiển thị trên hệ thống.
-Tài liệu đính kèm (Google Drive link) KHÔNG được xuất hiện trong file.</t>
+          <t>System tai ve mot file CSV successfully.
+File CSV co cac cot: Session ID, Session Name, Lesson Number, Description.
+Thong tin cac session khop voi danh sach display tren system.
+Tai lieu dinh kem (Google Drive link) KHONG duoc xuat hien trong file.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -3433,11 +3433,11 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7 (Export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="120" customHeight="1">
+          <t>Related to M07-F07, Rule 7 (Export)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="135" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>TC-M07-030</t>
@@ -3460,38 +3460,38 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Nhập CSV - Cập nhật thông tin Session đã tồn tại</t>
+          <t>Enter CSV - Cap nhat thong tin Session da ton tai</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống cập nhật chính xác tên, số bài và mô tả của session khi Session ID trong file CSV trùng khớp với session có sẵn.</t>
+          <t>Verify system cap nhat chinh xac ten, so bai va mo ta cua session khi Session ID trong file CSV trung khop voi session co san.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học với ID "S001" đã tồn tại dưới khóa học "Java Programming" có tên cũ là "OOP Intro".</t>
+          <t>User is logged in as Staff.
+Bai hoc voi ID "S001" da ton tai duoi course "Java Programming" co ten cu la "OOP Intro".</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID="S001"; Session Name="OOP Basics"; Lesson Number="1"; Description="Giới thiệu hướng đối tượng"</t>
+          <t>File CSV chua dong: Session ID="S001"; Session Name="OOP Basics"; Lesson Number="1"; Description="Gioi thieu huong doi tuong"</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV chứa dữ liệu cập nhật cho ID "S001".
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV chua du lieu cap nhat cho ID "S001".
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập dữ liệu thành công.
-Bài học có ID "S001" được cập nhật thành công với tên "OOP Basics", số bài "1", mô tả "Giới thiệu hướng đối tượng".
-Các tài liệu đính kèm trước đó của bài học này vẫn được giữ nguyên.</t>
+          <t>System display notification enter du lieu successfully.
+Bai hoc co ID "S001" duoc cap nhat successfully voi ten "OOP Basics", so bai "1", mo ta "Gioi thieu huong doi tuong".
+Cac tai lieu dinh kem truoc do cua session nay van duoc giu nguyen.</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr"/>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.1 (Existing Session)</t>
+          <t>Related to M07-F07, Rule 7.1 (Existing Session)</t>
         </is>
       </c>
     </row>
@@ -3534,38 +3534,38 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Nhập CSV - Tạo bài học mới khi để trống Session ID</t>
+          <t>Enter CSV - Create session moi khi blank Session ID</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống tự động tạo mới một bài học nếu cột Session ID trong dòng CSV bị bỏ trống.</t>
+          <t>Verify system tu dong create moi mot session neu cot Session ID trong dong CSV bi bo trong.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chọn khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Dang select course "Java Programming".</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID=""; Session Name="OOP Polymorphism"; Lesson Number="3"; Description="Tính đa hình"</t>
+          <t>File CSV chua dong: Session ID=""; Session Name="OOP Polymorphism"; Lesson Number="3"; Description="Tinh da hinh"</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV có cột ID để trống.
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV co cot ID blank.
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập dữ liệu thành công.
-Một bài học mới được tạo ra dưới khóa học "Java Programming" với tên "OOP Polymorphism", số bài học "3" và mô tả "Tính đa hình".
-Hệ thống tự động cấp phát một ID mới cho session này.</t>
+          <t>System display notification enter du lieu successfully.
+Mot session moi duoc create ra duoi course "Java Programming" voi ten "OOP Polymorphism", so session "3" va mo ta "Tinh da hinh".
+System tu dong cap phat mot ID moi cho session nay.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.2 (New Session)</t>
+          <t>Related to M07-F07, Rule 7.2 (New Session)</t>
         </is>
       </c>
     </row>
@@ -3608,37 +3608,37 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Nhập CSV - Tạo bài học mới khi Session ID không tồn tại trên hệ thống</t>
+          <t>Enter CSV - Create session moi khi Session ID khong ton tai tren system</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống tự động tạo mới bài học nếu Session ID trong CSV không trùng khớp với bất kỳ bài học hiện có nào.</t>
+          <t>Verify system tu dong create moi session neu Session ID trong CSV khong trung khop voi bat ky session hien co nao.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" không có bài học nào mang ID "S999".</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" khong co session nao mang ID "S999".</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID="S999"; Session Name="Exception Handling"; Lesson Number="4"; Description="Xử lý ngoại lệ"</t>
+          <t>File CSV chua dong: Session ID="S999"; Session Name="Exception Handling"; Lesson Number="4"; Description="Xu ly ngoai le"</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV chứa dòng có ID là "S999".
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV chua dong co ID la "S999".
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập dữ liệu thành công.
-Một bài học mới được tạo ra với ID mới được tạo hoặc cập nhật theo hệ thống, tên "Exception Handling" được gán dưới khóa học.</t>
+          <t>System display notification enter du lieu successfully.
+Mot session moi duoc create ra voi ID moi duoc create hoac cap nhat theo system, ten "Exception Handling" duoc gan duoi course.</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr"/>
@@ -3654,11 +3654,11 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.2 (New Session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="90" customHeight="1">
+          <t>Related to M07-F07, Rule 7.2 (New Session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="105" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TC-M07-033</t>
@@ -3681,37 +3681,37 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Nhập CSV - Các bài học hiện tại không có trong CSV sẽ giữ nguyên</t>
+          <t>Enter CSV - Cac session hien tai khong co trong CSV se giu nguyen</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống có bảo toàn các bài học sẵn có của khóa học nếu chúng không được liệt kê trong file CSV tải lên.</t>
+          <t>Verify whether system co bao toan cac session san co cua course neu chung khong duoc liet ke trong file CSV tai len.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang có 2 bài học sẵn có: "S001" và "S002".</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang co 2 session san co: "S001" va "S002".</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>File CSV chỉ chứa thông tin cập nhật cho bài học "S001". Bài học "S002" hoàn toàn không có trong file.</t>
+          <t>File CSV chi chua thong tin cap nhat cho session "S001". Bai hoc "S002" hoan toan khong co trong file.</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn "Nhập CSV" (Import CSV).
-2. Tải lên file CSV chỉ có thông tin cho bài học "S001".
-3. Nhấp "Xác nhận".</t>
+          <t>1. Nhap select "Enter CSV" (Import CSV).
+2. Upload file CSV chi co thong tin cho session "S001".
+3. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống thông báo nhập thành công.
-Bài học "S001" được cập nhật.
-Bài học "S002" vẫn tồn tại nguyên vẹn dưới khóa học "Java Programming" mà không bị xóa đi.</t>
+          <t>System notification enter successfully.
+Bai hoc "S001" duoc cap nhat.
+Bai hoc "S002" van ton tai nguyen ven duoi course "Java Programming" ma khong bi delete di.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.3 (Missing Sessions)</t>
+          <t>Related to M07-F07, Rule 7.3 (Missing Sessions)</t>
         </is>
       </c>
     </row>
@@ -3754,38 +3754,38 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Nhập CSV - Bỏ qua cột Materials trong file CSV tải lên</t>
+          <t>Enter CSV - Bo qua cot Materials trong file CSV tai len</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống có bỏ qua cột Materials và không ghi đè hoặc gây lỗi nếu file CSV chứa cột này.</t>
+          <t>Verify whether system co bo qua cot Materials va khong ghi de hoac gay error neu file CSV chua cot nay.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "S001" đang có sẵn một tài liệu đính kèm là "Slides".</t>
+          <t>User is logged in as Staff.
+Bai hoc "S001" dang co san mot tai lieu dinh kem la "Slides".</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>File CSV chứa các cột: Session ID, Session Name, Lesson Number, Description, Materials. Dòng dữ liệu: S001, OOP Basics, 1, Giới thiệu hướng đối tượng, https://drive.google.com/some-link-to-ignore</t>
+          <t>File CSV chua cac cot: Session ID, Session Name, Lesson Number, Description, Materials. Dong du lieu: S001, OOP Basics, 1, Gioi thieu huong doi tuong, https://drive.google.com/some-link-to-ignore</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học.
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV có chứa cột Materials với giá trị link bất kỳ.
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course.
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV co chua cot Materials voi gia tri link bat ky.
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập thành công.
-Thông tin Session được cập nhật.
-Tài liệu đính kèm "Slides" ban đầu của Session "S001" vẫn được giữ nguyên. Link trong cột Materials của file CSV hoàn toàn bị bỏ qua.</t>
+          <t>System display notification enter successfully.
+Thong tin Session duoc cap nhat.
+Tai lieu dinh kem "Slides" ban dau cua Session "S001" van duoc giu nguyen. Link trong cot Materials cua file CSV hoan toan bi bo qua.</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.4 (Materials Column)</t>
+          <t>Related to M07-F07, Rule 7.4 (Materials Column)</t>
         </is>
       </c>
     </row>
@@ -3828,36 +3828,36 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Nhập CSV thất bại do chọn sai định dạng tệp (không phải CSV)</t>
+          <t>Enter CSV failed do select sai format tep (not CSV)</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống từ chối tải lên và thông báo lỗi khi người dùng chọn tệp không phải đuôi .csv.</t>
+          <t>Verify system denies tai len va notification error khi user select tep not duoi .csv.</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Nhập CSV của khóa học.</t>
+          <t>User is logged in as Staff.
+Dang o interface Enter CSV cua course.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Tệp tin: document.docx hoặc image.png</t>
+          <t>Tep tin: document.docx hoac image.png</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn nút "Nhập CSV".
-2. Chọn tải lên tệp tin "document.docx".
-3. Nhấp nút "Xác nhận" hoặc hệ thống chặn ngay khi chọn tệp.</t>
+          <t>1. Nhap select nut "Enter CSV".
+2. Select tai len tep tin "document.docx".
+3. Nhap nut "Xac nhan" hoac system chan ngay khi select tep.</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối tệp tin và hiển thị thông báo lỗi định dạng tệp không hợp lệ (ví dụ: "Invalid file format. Please upload a CSV file.").
-Không có hành động nhập dữ liệu nào được thực hiện.</t>
+          <t>System denies tep tin va display notification error format tep khong hop le (e.g.: "Invalid file format. Please upload a CSV file.").
+Khong co hanh dong enter du lieu nao duoc thuc hien.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Error Handling (Mục 9)</t>
+          <t>Related to Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3900,36 +3900,36 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Nhập CSV thất bại đối với dòng thiếu thông tin Tên bài học</t>
+          <t>Enter CSV failed for dong thieu thong tin Ten session</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn việc tạo session mới qua CSV nếu dòng đó thiếu Tên bài học.</t>
+          <t>Verify system ngan chan viec create session moi qua CSV neu dong do thieu Ten session.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chọn khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Dang select course "Java Programming".</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID=""; Session Name=""; Lesson Number="5"; Description="Bài học thiếu tên"</t>
+          <t>File CSV chua dong: Session ID=""; Session Name=""; Lesson Number="5"; Description="Bai hoc thieu ten"</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn "Nhập CSV" (Import CSV).
-2. Tải lên file CSV chứa dòng dữ liệu lỗi nói trên.
-3. Nhấn "Xác nhận".</t>
+          <t>1. Nhap select "Enter CSV" (Import CSV).
+2. Upload file CSV chua dong du lieu error noi tren.
+3. Nhan "Xac nhan".</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi kiểm tra dữ liệu ở dòng tương ứng (ví dụ: "Row X: Session Name is required.").
-Dòng lỗi đó không được import vào hệ thống.</t>
+          <t>System bao error kiem tra du lieu o dong tuong ung (e.g.: "Row X: Session Name is required.").
+Dong error do khong duoc import vao system.</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3972,17 +3972,17 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Quyền truy cập - Staff truy cập và thao tác đầy đủ tính năng</t>
+          <t>Quyen access - Staff access va thao tac day du tinh nang</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản có email domain @passerellesnumeriques.org được cấp toàn quyền quản trị module.</t>
+          <t>Verify account co email domain @passerellesnumeriques.org duoc cap toan quyen quan tri module.</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập bằng Google OAuth với tài khoản staff@passerellesnumeriques.org.</t>
+          <t>Nguoi dung da log in bang Google OAuth voi account staff@passerellesnumeriques.org.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3992,14 +3992,14 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cập vào trang Quản lý Tài liệu học tập.
-2. Thực hiện các thao tác: Đổi tên Category, Thêm khóa học, Xóa bài học, Nhập/Xuất CSV.</t>
+          <t>1. Truy cap vao trang Quan ly Tai lieu hoc tap.
+2. Thuc hien cac thao tac: Rename Category, Add course, Delete session, Enter/Xuat CSV.</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Người dùng truy cập thành công.
-Tất cả các nút chức năng hoạt động bình thường mà không bị chặn quyền.</t>
+          <t>Nguoi dung access successfully.
+Tat ca cac nut chuc nang hoat dong binh thuong ma khong bi chan quyen.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs/docs.md Mục 4 (User Roles)</t>
+          <t>Related to Docs/docs.md Section 4 (User Roles)</t>
         </is>
       </c>
     </row>
@@ -4042,17 +4042,17 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Quyền truy cập - Học viên (Student) bị hạn chế các quyền quản lý</t>
+          <t>Quyen access - Hoc vien (Student) bi han che cac quyen quan ly</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản học viên có email domain @student.passerellesnumeriques.org không thể thực hiện các thao tác quản lý (Thêm/Sửa/Xóa/Archive/Import/Export) trên module.</t>
+          <t>Verify account student co email domain @student.passerellesnumeriques.org cannot thuc hien cac thao tac quan ly (Add/Sua/Delete/Archive/Import/Export) tren module.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập bằng Google OAuth với tài khoản student@student.passerellesnumeriques.org.</t>
+          <t>Nguoi dung da log in bang Google OAuth voi account student@student.passerellesnumeriques.org.</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -4062,15 +4062,15 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>1. Cố gắng truy cập trực tiếp vào đường dẫn Quản lý Tài liệu học tập (nếu có), hoặc kiểm tra giao diện Student Portal.
-2. Quan sát sự tồn tại của các nút chức năng đổi tên, thêm khóa học, xóa bài học, import CSV.</t>
+          <t>1. Co gang access truc tiep vao duong dan Quan ly Tai lieu hoc tap (neu co), hoac kiem tra interface Student Portal.
+2. Observe su ton tai cua cac nut chuc nang doi ten, add course, delete session, import CSV.</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>Học viên không có quyền truy cập vào trang quản trị Staff.
-Không hiển thị các nút chức năng quản lý tài liệu học tập trên màn hình dành cho học viên.
-Hệ thống hiển thị thông báo lỗi hoặc từ chối truy cập (Access Denied) nếu cố truy cập qua URL trực tiếp.</t>
+          <t>Hoc vien khong co quyen access trang quan tri Staff.
+Khong display cac nut chuc nang quan ly tai lieu hoc tap tren man hinh danh cho student.
+System display notification error hoac denies access (Access Denied) neu co access qua URL truc tiep.</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs/docs.md Mục 4 (User Roles)</t>
+          <t>Related to Docs/docs.md Section 4 (User Roles)</t>
         </is>
       </c>
     </row>
@@ -4113,17 +4113,17 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Quyền truy cập - Domain lạ bị từ chối truy cập hệ thống</t>
+          <t>Quyen access - Domain la bi denies access system</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống từ chối truy cập ngay lập tức đối với email không thuộc 2 domain được cấu hình.</t>
+          <t>Verify system denies access ngay lap tuc for email khong thuoc 2 domain duoc cau hinh.</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập bằng Google OAuth với tài khoản user@gmail.com.</t>
+          <t>Nguoi dung da log in bang Google OAuth voi account user@gmail.com.</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -4133,13 +4133,13 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>1. Cố gắng truy cập vào hệ thống Academic Portal.</t>
+          <t>1. Co gang access system Academic Portal.</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị trang từ chối truy cập (Access Denied).
-Không hiển thị bất kỳ thông tin nào về các danh mục tài liệu hoặc khóa học.</t>
+          <t>System display trang denies access (Access Denied).
+Khong display bat ky thong tin nao ve cac category tai lieu hoac course.</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs/docs.md Mục 4 &amp; Mục 6 (Authentication Flow)</t>
+          <t>Related to Docs/docs.md Section 4 &amp; Section 6 (Authentication Flow)</t>
         </is>
       </c>
     </row>
@@ -4182,18 +4182,18 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra ẩn tự động tất cả Session/Exam con khi Lưu trữ khóa học</t>
+          <t>Verify an tu dong tat ca Session/Exam con khi Archive course</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Xác minh rằng khi lưu trữ một khóa học, tất cả các bài học (session) và bài kiểm tra (exam) thuộc khóa học đó tự động biến mất khỏi giao diện chung của người dùng, nhưng dữ liệu vẫn tồn tại trong cơ sở dữ liệu.</t>
+          <t>Verify rang khi archive mot course, tat ca cac session (session) va exam (exam) thuoc course do tu dong bien mat khoi interface chung cua user, nhung du lieu van ton tai trong co so du lieu.</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang hoạt động và có bài học "Session 01" cùng bài kiểm tra "Midterm Exam" đang hiển thị.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang hoat dong va co session "Session 01" cung exam "Midterm Exam" dang display.</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -4203,15 +4203,15 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>1. Thực hiện lưu trữ khóa học "Java Programming".
-2. Truy cập hoặc kiểm tra danh sách bài học và bài kiểm tra trên giao diện hiển thị tài liệu chung.</t>
+          <t>1. Thuc hien archive course "Java Programming".
+2. Truy cap hoac kiem tra danh sach session va exam tren interface display tai lieu chung.</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Khóa học chuyển sang trạng thái đã lưu trữ.
-Bài học "Session 01" và bài kiểm tra "Midterm Exam" không còn xuất hiện trên giao diện hiển thị tài liệu học tập chung.
-Kiểm tra cơ sở dữ liệu để đảm bảo các bản ghi này vẫn tồn tại.</t>
+          <t>Khoa hoc chuyen sang status da archive.
+Bai hoc "Session 01" va exam "Midterm Exam" khong con xuat hien tren interface display tai lieu hoc tap chung.
+Verify co so du lieu de dam bao cac ban ghi nay van ton tai.</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr"/>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="N41" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -4254,18 +4254,18 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra khôi phục hiển thị tất cả Session/Exam con khi Khôi phục khóa học</t>
+          <t>Verify khoi phuc display tat ca Session/Exam con khi Khoi phuc course</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Xác minh rằng khi khôi phục một khóa học đã lưu trữ, tất cả các bài học (session) và bài kiểm tra (exam) thuộc khóa học đó tự động hiển thị trở lại trên giao diện.</t>
+          <t>Verify rang khi khoi phuc mot course da archive, tat ca cac session (session) va exam (exam) thuoc course do tu dong display tro lai tren interface.</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang ở trạng thái Lưu trữ (Archived), các bài học và bài kiểm tra con đang bị ẩn hiển thị.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang o status Archive (Archived), cac session va exam con dang bi an display.</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -4275,14 +4275,14 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>1. Thực hiện khôi phục khóa học "Java Programming".
-2. Truy cập vào giao diện hiển thị bài học và bài kiểm tra của khóa học này.</t>
+          <t>1. Thuc hien khoi phuc course "Java Programming".
+2. Truy cap vao interface display session va exam cua course nay.</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Khóa học chuyển sang trạng thái Hoạt động (Active).
-Bài học "Session 01" và bài kiểm tra "Midterm Exam" tự động xuất hiện trở lại trên giao diện hiển thị và có thể xem/chỉnh sửa bình thường.</t>
+          <t>Khoa hoc chuyen sang status Hoat dong (Active).
+Bai hoc "Session 01" va exam "Midterm Exam" tu dong xuat hien tro lai tren interface display va can xem/edit binh thuong.</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.3</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module07_test_cases.xlsx
+++ b/Tests/excel/module07_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Module07" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module07'!$A$1:$N$42</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,21 +429,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$16</f>
+              <f>'Report'!$A$9:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$C$9:$C$16</f>
+              <f>'Report'!$C$9:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -456,21 +456,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$16</f>
+              <f>'Report'!$A$9:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$D$9:$D$16</f>
+              <f>'Report'!$D$9:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -483,21 +483,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$16</f>
+              <f>'Report'!$A$9:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$E$9:$E$16</f>
+              <f>'Report'!$E$9:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -938,23 +938,23 @@
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="14">
-        <f>COUNTA(A9:A16)</f>
+        <f>COUNTA(A9:A15)</f>
         <v/>
       </c>
       <c r="B5" s="15">
-        <f>F17</f>
+        <f>F16</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIF(C9:C16, "&gt;0")</f>
+        <f>COUNTIF(C9:C15, "&gt;0")</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>COUNTIFS(C9:C16, 0, D9:D16, "&gt;0")</f>
+        <f>COUNTIFS(C9:C15, 0, D9:D15, "&gt;0")</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>COUNTIFS(C9:C16, 0, D9:D16, 0, E9:E16, "&gt;0")</f>
+        <f>COUNTIFS(C9:C15, 0, D9:D15, 0, E9:E15, "&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F03</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="C10" s="30">
@@ -1056,12 +1056,12 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>M07-F03</t>
+          <t>M07-F04</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Course Archiving / Restoring</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="C11" s="24">
@@ -1084,12 +1084,12 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
-          <t>M07-F04</t>
+          <t>M07-F05</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Session Deletion</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="C12" s="30">
@@ -1112,12 +1112,12 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>M07-F05</t>
+          <t>M07-F06</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Exam Deletion</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="C13" s="24">
@@ -1140,12 +1140,12 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>M07-F06</t>
+          <t>M07-F07</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Material Attachment</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="C14" s="30">
@@ -1168,12 +1168,12 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>M07-F07</t>
+          <t>M07-F08</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="C15" s="24">
@@ -1193,58 +1193,30 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>M07-SEC</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>Access Control &amp; Security</t>
-        </is>
-      </c>
-      <c r="C16" s="30">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A16, 'Module07'!$M$2:$M$42, "High")</f>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="35">
+        <f>COUNTA(A9:A15)&amp;" Features"</f>
         <v/>
       </c>
-      <c r="D16" s="31">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A16, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="C16" s="34">
+        <f>SUM(C9:C15)</f>
         <v/>
       </c>
-      <c r="E16" s="32">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A16, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="D16" s="34">
+        <f>SUM(D9:D15)</f>
         <v/>
       </c>
-      <c r="F16" s="33">
-        <f>SUM(C16:E16)</f>
+      <c r="E16" s="34">
+        <f>SUM(E9:E15)</f>
         <v/>
       </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B17" s="35">
-        <f>COUNTA(A9:A16)&amp;" Features"</f>
-        <v/>
-      </c>
-      <c r="C17" s="34">
-        <f>SUM(C9:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="34">
-        <f>SUM(D9:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="34">
-        <f>SUM(E9:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="34">
-        <f>SUM(F9:F16)</f>
+      <c r="F16" s="34">
+        <f>SUM(F9:F15)</f>
         <v/>
       </c>
     </row>
@@ -1359,7 +1331,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1374,12 +1346,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Rename Category with a valid name</t>
+          <t>Rename Category with a Valid Name</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for doi ten category (Category) khi enter ten moi hop le.</t>
+          <t>Verify functionality for renaming a category when entering a valid new name.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -1390,22 +1362,21 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>CategoryOldName="IT"; CategoryNewName="Information Technology"</t>
+          <t>OldCategoryName="General"; NewCategoryName="Foundations"</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Nhap select category "IT".
-2. Nhap nut "Rename" (Rename).
-3. Enter ten moi la "Information Technology".
-4. Nhap "Save" (Save).</t>
+          <t>1. Select Category "General";
+2. Click Rename Category button;
+3. Enter new name as "Foundations";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>System display notification cap nhat successfully.
-Ten category duoc thay doi thanh "Information Technology" tren interface.
-Cac course ben trong category van giu nguyen.</t>
+          <t>Category renamed successfully.
+New category name "Foundations" is updated and displayed on UI.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1421,11 +1392,11 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F02, Rule 5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="75" customHeight="1">
+          <t>Related Requirement: M07-F02, Rule 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>TC-M07-002</t>
@@ -1433,7 +1404,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -1448,35 +1419,35 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Category rename fails due to empty name</t>
+          <t>Category Rename Fails Due to Empty Name</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Verify system bao error va ngan chan viec doi ten category thanh rong.</t>
+          <t>Verify system displays error and prevents renaming category when new name is empty.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Currently on Rename Category interface.</t>
+Currently on Rename Category dialog.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>CategoryNewName=""</t>
+          <t>NewCategoryName=""</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Delete toan bo noi dung trong o enter ten category.
-2. Nhap nut "Save" (Save).</t>
+          <t>1. Leave new Category Name field empty;
+2. Click Save button.</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>System display notification error requires enter ten category (e.g.: "Category Name is required.").
-Ten category cu khong bi thay doi.</t>
+          <t>System blocks action.
+Validation error message appears: "Category Name cannot be empty."</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1492,7 +1463,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
+          <t>Related Requirement: M07-F02, Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1475,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1519,34 +1490,34 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Verify Archive and Delete functions are not supported for Category</t>
+          <t>Verify Archive and Delete Functions Are Not Supported for Category</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Verify system not displayed cac chuc nang Archive (Archive) va Delete (Delete) for category.</t>
+          <t>Verify system does not support archive or delete operations on categories.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Currently on Training Materials Management interface.</t>
+Viewing Category menu.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>CategoryName="English"</t>
+          <t>CategoryName="Foundations"</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Nhap select category "English".
-2. Observe cac nut chuc nang va menu ngu cphoto lien quan den category.</t>
+          <t>1. Open options menu for Category "Foundations";
+2. Check for Archive or Delete options.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Khong display nut hoac tuy select "Delete" (Delete) hoac "Archive" (Archive) for category.</t>
+          <t>Archive and Delete buttons are not present in Category context menu.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1562,11 +1533,11 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F02, Rule 5.1, Out of Scope (Section 13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>Related Requirement: M07-F02, Business Rules 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>TC-M07-004</t>
@@ -1574,48 +1545,48 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F02</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Category Management</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Verify default Categories exist in system</t>
+          <t>Verify Default Categories Exist in System</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Verify 5 category mac dinh duoc create san khi system hoat dong.</t>
+          <t>Verify system contains default fixed categories upon initialization.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Currently on Training Materials Management interface.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>DefaultCategories=["IT", "English", "Professional Skills"]</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Observe danh sach cac category display tren man hinh.</t>
+          <t>1. Access Training Materials page;
+2. Check category sidebar/tabs.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>System display day du 5 category mac dinh: "IT", "English", "PLT", "DA", va "Workshops".</t>
+          <t>Default categories "IT", "English", and "Professional Skills" are present in system.</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1631,7 +1602,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F01, Section 3 (Default Categories)</t>
+          <t>Related Requirement: M07-F02, Business Rules 6.2</t>
         </is>
       </c>
     </row>
@@ -1643,52 +1614,52 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F03</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Create new course with valid information</t>
+          <t>Create New Course with Valid Information</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for create new course duoi mot category khi enter day du thong tin hop le.</t>
+          <t>Verify functionality for creating a new course within a category.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Currently on Training Materials Management interface.</t>
+Category "IT" exists.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Category="IT"; CourseName="Java Programming"</t>
+          <t>Category="IT"; CourseName="Web Development"</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Select category "IT".
-2. Nhap nut "Create course" (Create Course).
-3. Enter ten course la "Java Programming".
-4. Nhap "Save" (Save).</t>
+          <t>1. Select Category "IT";
+2. Click Create New Course button;
+3. Enter Course Name as "Web Development";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>System display notification create successfully.
-Khoa hoc "Java Programming" display duoi category "IT".</t>
+          <t>Course created successfully.
+New course "Web Development" appears under category "IT".</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1704,11 +1675,11 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F01, Rule 5.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>Related Requirement: M07-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>TC-M07-006</t>
@@ -1716,7 +1687,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1726,40 +1697,39 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Course Archiving / Restoring</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>New course creation fails due to empty name</t>
+          <t>New Course Creation Fails Due to Empty Name</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Verify system bao error va ngan chan create course neu ten course trong.</t>
+          <t>Verify system displays error when course name is empty.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Currently on Create New Course interface.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Category="IT"; CourseName=""</t>
+          <t>CourseName=""</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. De trong truong Ten course.
-2. Nhap "Save" (Save).</t>
+          <t>1. Leave Course Name field empty;
+2. Click Save button.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>System display error requires enter ten course (e.g.: "Course Name is required.").
-Khoa hoc moi khong duoc create.</t>
+          <t>System blocks action.
+Validation error appears: "Course Name is required."</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1775,7 +1745,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
+          <t>Related Requirement: M07-F03, Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -1787,52 +1757,51 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F03</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Edit course name with valid information</t>
+          <t>Edit Course Name with Valid Information</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for edit ten course successfully.</t>
+          <t>Verify functionality for updating course name.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Currently on Training Materials Management interface. Khoa hoc "Java Programming" da ton tai.</t>
+Course "Web Development" exists.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>CourseOldName="Java Programming"; CourseNewName="Advanced Java Programming"</t>
+          <t>OldCourseName="Web Development"; NewCourseName="Frontend Development"</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Select course "Java Programming".
-2. Nhap select "Edit" (Edit).
-3. Thay doi ten course thanh "Advanced Java Programming".
-4. Nhap "Save" (Save).</t>
+          <t>1. Select Course "Web Development";
+2. Click Edit Course button;
+3. Change name to "Frontend Development";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>System display notification save successfully.
-Ten course cap nhat thanh "Advanced Java Programming" tren man hinh.</t>
+          <t>Course name updated successfully to "Frontend Development".</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1848,11 +1817,11 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F01, Rule 5.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>Related Requirement: M07-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>TC-M07-008</t>
@@ -1860,7 +1829,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1870,41 +1839,40 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Course Archiving / Restoring</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Archive course (Archive Course)</t>
+          <t>Archive Active Course</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Verify functionality for archive course.</t>
+          <t>Verify functionality for archiving an active course.</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" dang o status Hoat dong (Active) va co cac session/exam ben duoi.</t>
+Course "Frontend Development" is Active.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"</t>
+          <t>CourseName="Frontend Development"</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Nhap select course "Java Programming".
-2. Nhap select nut "Archive" (Archive).
-3. Xac nhan archive neu system requires.</t>
+          <t>1. Click Archive button for course "Frontend Development";
+2. Confirm archiving in popup dialog.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>System display notification archive successfully.
-Khoa hoc thay doi status sang da archive (Archived) va bi an di hoac display as archive tren man hinh quan ly.</t>
+          <t>Course status changes to Archived.
+Course is hidden from Active list and moved to Archived tab.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1920,11 +1888,11 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F03, Rule 5.2, Rule 5.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
+          <t>Related Requirement: M07-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC-M07-009</t>
@@ -1932,7 +1900,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1942,41 +1910,41 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Course Archiving / Restoring</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Khoi phuc course da archive (Restore Course)</t>
+          <t>Restore Archived Course</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for khoi phuc mot course da bi archive.</t>
+          <t>Verify functionality for restoring a previously archived course.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" dang o status Archive (Archived).</t>
+Course "Frontend Development" is Archived.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"</t>
+          <t>CourseName="Frontend Development"</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Tim va select course "Java Programming" trong danh sach archive.
-2. Nhap select nut "Khoi phuc" (Restore).
-3. Xac nhan khoi phuc neu system requires.</t>
+          <t>1. Navigate to Archived Courses tab;
+2. Click Restore button for course "Frontend Development";
+3. Confirm restoration.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>System display notification khoi phuc successfully.
-Khoa hoc tro lai status hoat dong binh thuong.</t>
+          <t>Course status changes back to Active.
+Course reappears in active course list.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1992,11 +1960,11 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F03, Rule 5.2, Rule 5.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Related Requirement: M07-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>TC-M07-010</t>
@@ -2004,7 +1972,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2014,39 +1982,39 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Course Archiving / Restoring</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Verify khong ho tro permanently deleted course</t>
+          <t>Verify Permanent Deletion Is Not Supported for Course</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Verify system khong allows permanently deleted course khoi co so du lieu.</t>
+          <t>Verify system does not provide permanent deletion for courses.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Currently on Training Materials Management interface.</t>
+Viewing course options menu.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"</t>
+          <t>CourseName="Frontend Development"</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Select course "Java Programming".
-2. Verify cac nut chuc nang va menu hanh dong lien quan den course.</t>
+          <t>1. Open course action menu;
+2. Check available options.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Khong co tuy select "Delete vinh vien" hoac "Delete" cho course, chi co tuy select "Archive" (Archive).</t>
+          <t>Permanent Delete button is not present for courses (only Archive is supported).</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2062,11 +2030,11 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Related to Rule 5.2 (Permanent deletion is not allowed), Out of Scope (Section 13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="135" customHeight="1">
+          <t>Related Requirement: M07-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC-M07-011</t>
@@ -2074,52 +2042,52 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F04</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Create session (Session) moi voi thong tin hop le</t>
+          <t>Create New Session with Valid Information</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for create session moi duoi mot course hoat dong.</t>
+          <t>Verify functionality for creating a new learning session inside a course.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" dang hoat dong.</t>
+Course "Web Development" exists.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"; SessionName="Session 01: OOP Basics"; LessonNumber=1; Description="Gioi thieu ve lap trinh huong doi tuong"</t>
+          <t>CourseName="Web Development"; SessionName="Session 1: HTML Basics"</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Select course "Java Programming".
-2. Nhap nut "Add session" (Add Session).
-3. Enter Ten session la "Session 01: OOP Basics", so session la "1", mo ta la "Gioi thieu ve lap trinh huong doi tuong".
-4. Nhap "Save" (Save).</t>
+          <t>1. Open Course "Web Development";
+2. Click Add Session button;
+3. Enter Session Name as "Session 1: HTML Basics";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>System display notification create successfully.
-Session moi display duoi course "Java Programming".</t>
+          <t>Session created successfully.
+"Session 1: HTML Basics" appears inside course.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2135,11 +2103,11 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F01, Rule 5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
+          <t>Related Requirement: M07-F04, Business Rules 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>TC-M07-012</t>
@@ -2147,7 +2115,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2157,41 +2125,39 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Session Deletion</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Create session moi failed due to empty name session</t>
+          <t>New Session Creation Fails Due to Empty Session Name</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Verify system bao error va ngan chan create session neu ten session trong.</t>
+          <t>Verify system displays error when session name is empty.</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang o interface Add session moi.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"; SessionName=""; LessonNumber=1</t>
+          <t>SessionName=""</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. De trong truong Ten session.
-2. Enter cac truong thong tin khac hop le.
-3. Nhap "Save" (Save).</t>
+          <t>1. Leave Session Name field empty;
+2. Click Save button.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>System display notification error requires enter Ten session (e.g.: "Session Name is required.").
-Bai hoc moi khong duoc create.</t>
+          <t>System blocks action.
+Validation error appears: "Session Name is required."</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2207,11 +2173,11 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="135" customHeight="1">
+          <t>Related Requirement: M07-F04, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC-M07-013</t>
@@ -2219,52 +2185,50 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F04</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Edit chi tiet session (Edit Session)</t>
+          <t>Edit Session Details</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for sua thong tin session successfully.</t>
+          <t>Verify functionality for updating session title/details.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Bai hoc "Session 01: OOP Basics" da ton tai duoi course "Java Programming".</t>
+Session "Session 1: HTML Basics" exists.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>SessionOldName="Session 01: OOP Basics"; SessionNewName="Session 01: Advanced OOP Basics"; LessonNumber=2; Description="Mo ta moi"</t>
+          <t>OldSessionName="Session 1: HTML Basics"; NewSessionName="Session 1: HTML &amp; CSS Fundamentals"</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Select session "Session 01: OOP Basics".
-2. Nhap select "Edit" (Edit).
-3. Sua Ten session thanh "Session 01: Advanced OOP Basics", Lesson Number thanh "2", Description thanh "Mo ta moi".
-4. Nhap "Save" (Save).</t>
+          <t>1. Click Edit icon on session;
+2. Update Session Name to "Session 1: HTML &amp; CSS Fundamentals";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>System display notification save successfully.
-Thong tin session display thay doi moi tuong ung tren interface.</t>
+          <t>Session details updated successfully.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2280,11 +2244,11 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F01, Rule 5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
+          <t>Related Requirement: M07-F04, Business Rules 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TC-M07-014</t>
@@ -2292,7 +2256,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -2302,43 +2266,39 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Session Deletion</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Delete vinh vien session (Delete Session)</t>
+          <t>Permanently Delete Session</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Verify functionality for permanently deleted mot session va cac tai lieu dinh kem ben duoi no.</t>
+          <t>Verify functionality for permanently deleting a session.</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Bai hoc "Session 01: OOP Basics" dang ton tai va co tai lieu dinh kem.</t>
+Session "Session 1" exists.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>SessionName="Session 01: OOP Basics"</t>
+          <t>SessionName="Session 1"</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Select session "Session 01: OOP Basics".
-2. Nhap select nut "Delete" (Delete).
-3. System display hop thoai requires xac nhan permanently deleted.
-4. Nhap "Dong y" (Confirm).</t>
+          <t>1. Click Delete icon on session;
+2. Confirm permanent deletion in confirmation dialog.</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>System display notification delete successfully.
-Bai hoc va cac tai lieu dinh kem bi permanently deleted khoi system.
-Hanh dong cannot hoan tac.</t>
+          <t>Session and all attached materials are permanently deleted from system.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2354,11 +2314,11 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F04, Rule 5.4, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="105" customHeight="1">
+          <t>Related Requirement: M07-F04, Business Rules 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-M07-015</t>
@@ -2366,7 +2326,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2376,42 +2336,40 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Session Deletion</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Huy bo thao tac delete session</t>
+          <t>Cancel Session Deletion Operation</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Verify whether khi huy xac nhan delete, session van duoc giu lai.</t>
+          <t>Verify clicking Cancel in session deletion dialog preserves session without deleting.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Bai hoc "Session 01: OOP Basics" dang ton tai.</t>
+Session deletion modal open.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>SessionName="Session 01: OOP Basics"</t>
+          <t>Action="Cancel Deletion"</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Select session "Session 01: OOP Basics".
-2. Nhap select nut "Delete" (Delete).
-3. System display hop thoai xac nhan.
-4. Nhap select "Huy" (Cancel).</t>
+          <t>1. Click Delete icon on session;
+2. In confirmation dialog, click Cancel button.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Hop thoai xac nhan dong lai.
-Bai hoc "Session 01: OOP Basics" van ton tai trong danh sach va khong bi delete.</t>
+          <t>Dialog closes.
+Session remains intact in course.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2427,11 +2385,11 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Related to Rule 5.4, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>Related Requirement: M07-F04, UI Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M07-016</t>
@@ -2439,7 +2397,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -2449,39 +2407,37 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Session Deletion</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Verify khong ho tro archive session</t>
+          <t>Verify Archive Operation Is Not Supported for Session</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Verify system khong allows archive session, chi can permanently deleted.</t>
+          <t>Verify system does not support archiving individual sessions.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang o interface Quan ly Bai hoc.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>SessionName="Session 01: OOP Basics"</t>
+          <t>SessionName="Session 1"</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Select session "Session 01: OOP Basics".
-2. Verify cac nut chuc nang hanh dong tren session.</t>
+          <t>1. Check available actions on session.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Khong xuat hien tuy select "Archive" (Archive) for session. Chi ho tro create, sua va permanently deleted.</t>
+          <t>Archive button is not available for sessions (only Delete is supported).</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2497,11 +2453,11 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Related to Rule 5.4, Out of Scope (Section 13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="105" customHeight="1">
+          <t>Related Requirement: M07-F04, Business Rules 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC-M07-017</t>
@@ -2509,52 +2465,52 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F05</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Create exam (Exam) moi voi thong tin hop le</t>
+          <t>Create New Exam with Valid Information</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for create exam moi duoi mot course dang hoat dong.</t>
+          <t>Verify functionality for creating a new exam item inside a course.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" dang hoat dong.</t>
+Course "Web Development" exists.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"; ExamName="Midterm Exam"</t>
+          <t>CourseName="Web Development"; ExamName="Midterm Exam"</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Select course "Java Programming".
-2. Nhap nut "Add exam" (Add Exam).
-3. Enter Ten exam la "Midterm Exam".
-4. Nhap "Save" (Save).</t>
+          <t>1. Open Course "Web Development";
+2. Click Add Exam button;
+3. Enter Exam Name as "Midterm Exam";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>System display notification create successfully.
-Bai kiem tra "Midterm Exam" display duoi course "Java Programming".</t>
+          <t>Exam created successfully.
+"Midterm Exam" displays in exam section of course.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2570,11 +2526,11 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F01, Rule 5.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="75" customHeight="1">
+          <t>Related Requirement: M07-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>TC-M07-018</t>
@@ -2582,7 +2538,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2592,40 +2548,39 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Exam Deletion</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Create exam moi failed due to empty name</t>
+          <t>New Exam Creation Fails Due to Empty Name</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Verify system ngan chan va bao error neu ten exam trong.</t>
+          <t>Verify system displays error when exam name is empty.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang o interface Add exam moi.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"; ExamName=""</t>
+          <t>ExamName=""</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. De trong truong Ten exam.
-2. Nhap "Save" (Save).</t>
+          <t>1. Leave Exam Name field empty;
+2. Click Save button.</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>System display notification error requires enter Ten exam (e.g.: "Exam Name is required.").
-Bai kiem tra khong duoc create.</t>
+          <t>System blocks action.
+Validation error appears: "Exam Name is required."</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2641,11 +2596,11 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="105" customHeight="1">
+          <t>Related Requirement: M07-F05, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-M07-019</t>
@@ -2653,52 +2608,50 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>M07-F01</t>
+          <t>M07-F05</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Three-tier Hierarchy</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Edit chi tiet exam (Edit Exam)</t>
+          <t>Edit Exam Details</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for thay doi ten exam successfully.</t>
+          <t>Verify functionality for updating exam title/details.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Bai kiem tra "Midterm Exam" da ton tai duoi course "Java Programming".</t>
+Exam "Midterm Exam" exists.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>ExamOldName="Midterm Exam"; ExamNewName="Midterm Practical Exam"</t>
+          <t>OldExamName="Midterm Exam"; NewExamName="Midterm Practical Exam"</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Select exam "Midterm Exam".
-2. Nhap select "Edit" (Edit).
-3. Thay doi ten thanh "Midterm Practical Exam".
-4. Nhap "Save" (Save).</t>
+          <t>1. Click Edit icon on exam;
+2. Update Exam Name to "Midterm Practical Exam";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>System display notification save successfully.
-Ten exam duoc cap nhat thanh "Midterm Practical Exam" tren interface.</t>
+          <t>Exam details updated successfully.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2714,11 +2667,11 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F01, Rule 5.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+          <t>Related Requirement: M07-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>TC-M07-020</t>
@@ -2726,7 +2679,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2736,23 +2689,23 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Exam Deletion</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Delete vinh vien exam (Delete Exam)</t>
+          <t>Permanently Delete Exam</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Verify functionality for permanently deleted mot exam va cac tai lieu dinh kem ben duoi no.</t>
+          <t>Verify functionality for permanently deleting an exam.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Bai kiem tra "Midterm Exam" dang ton tai va co tai lieu dinh kem.</t>
+Exam "Midterm Exam" exists.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -2762,16 +2715,13 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Select exam "Midterm Exam".
-2. Nhap nut "Delete" (Delete).
-3. Xac nhan tren hop thoai display bang cach select "Dong y" (Confirm).</t>
+          <t>1. Click Delete icon on exam;
+2. Confirm permanent deletion in confirmation dialog.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>System display notification delete successfully.
-Bai kiem tra va cac tai lieu dinh kem bi permanently deleted khoi system.
-Hanh dong cannot hoan tac.</t>
+          <t>Exam and all attached exam materials are permanently deleted from system.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2787,11 +2737,11 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F05, Rule 5.5, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="75" customHeight="1">
+          <t>Related Requirement: M07-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>TC-M07-021</t>
@@ -2799,7 +2749,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2809,41 +2759,40 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Exam Deletion</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Huy bo thao tac delete exam</t>
+          <t>Cancel Exam Deletion Operation</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Verify whether exam khong bi delete khi huy xac nhan.</t>
+          <t>Verify clicking Cancel in exam deletion dialog preserves exam without deleting.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Bai kiem tra "Midterm Exam" dang ton tai.</t>
+Exam deletion modal open.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>ExamName="Midterm Exam"</t>
+          <t>Action="Cancel Deletion"</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>1. Select exam "Midterm Exam".
-2. Nhap nut "Delete" (Delete).
-3. Tren hop thoai xac nhan, select "Huy" (Cancel).</t>
+          <t>1. Click Delete icon on exam;
+2. In confirmation dialog, click Cancel button.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Hop thoai dong lai.
-Bai kiem tra "Midterm Exam" van ton tai binh thuong.</t>
+          <t>Dialog closes.
+Exam remains intact in course.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2859,11 +2808,11 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Related to Rule 5.5, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>Related Requirement: M07-F05, UI Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t>TC-M07-022</t>
@@ -2871,7 +2820,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2881,23 +2830,22 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Exam Deletion</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Verify khong ho tro archive exam</t>
+          <t>Verify Archive Operation Is Not Supported for Exam</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Verify system khong allows archive exam, chi can permanently deleted.</t>
+          <t>Verify system does not support archiving individual exams.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang o interface Quan ly Bai kiem tra.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -2907,13 +2855,12 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>1. Select exam "Midterm Exam".
-2. Verify cac nut hanh dong tren exam.</t>
+          <t>1. Check available actions on exam.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Khong xuat hien tuy select "Archive" (Archive) for exam.</t>
+          <t>Archive button is not available for exams (only Delete is supported).</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
@@ -2929,11 +2876,11 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>Related to Rule 5.5, Out of Scope (Section 13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
+          <t>Related Requirement: M07-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TC-M07-023</t>
@@ -2941,7 +2888,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2951,41 +2898,41 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Material Attachment</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Dinh kem mot tai lieu hop le vao Session/Exam</t>
+          <t>Attach a Valid Document Link to Session/Exam</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for dinh kem tai lieu successfully khi enter du nhan va link Google Drive dung format.</t>
+          <t>Verify functionality for attaching a valid Google Drive material link with a label.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Dang create hoac sua mot Session hoac Exam.</t>
+Session or Exam exists.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Label="Slides"; URL="https://drive.google.com/file/d/1A2B3C4D5E/view"</t>
+          <t>Label="Lecture Slides"; Url="https://drive.google.com/file/d/123/view"</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>1. O phan dinh kem tai lieu (Material Attachments), enter Nhan (Label) la "Slides".
-2. Enter URL la "https://drive.google.com/file/d/1A2B3C4D5E/view".
-3. Nhan "Save" (Save).</t>
+          <t>1. Open Attach Material dialog for Session/Exam;
+2. Enter Label as "Lecture Slides";
+3. Enter URL as "https://drive.google.com/file/d/123/view";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Tai lieu duoc save successfully.
-Thong tin dinh kem display chinh xac duoi Session/Exam.</t>
+          <t>Material link is attached successfully and clickable on UI.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -3001,11 +2948,11 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F06, Section 6 (Material Attachments)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="150" customHeight="1">
+          <t>Related Requirement: M07-F06, Business Rules 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="75" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>TC-M07-024</t>
@@ -3013,7 +2960,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3023,41 +2970,39 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Material Attachment</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Dinh kem nhieu tai lieu hop le vao Session/Exam</t>
+          <t>Attach Multiple Valid Document Links to Session/Exam</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Verify viec dinh kem dong thoi nhieu tai lieu hop le vao cung mot session hoac exam.</t>
+          <t>Verify functionality for attaching multiple document links simultaneously.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang create hoac sua mot Session hoac Exam.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Attachment1: Label="Slides", URL="https://drive.google.com/file/d/111/view"; Attachment2: Label="Homework", URL="https://drive.google.com/file/d/222/view"</t>
+          <t>Materials=[{Label: "Slides", Url: "https://drive.google.com/file/1"}, {Label: "Exercise", Url: "https://drive.google.com/file/2"}]</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>1. O dong tai lieu thu nhat, enter Nhan "Slides" and URL "https://drive.google.com/file/d/111/view".
-2. Nhap add dong moi.
-3. O dong tai lieu Monday, enter Nhan "Homework" and URL "https://drive.google.com/file/d/222/view".
-4. Nhan "Save" (Save).</t>
+          <t>1. Add multiple material rows;
+2. Enter valid Labels and Google Drive URLs;
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>Ca hai tai lieu dinh kem deu duoc save successfully va display day du tren interface.</t>
+          <t>All material links are attached and displayed under session/exam.</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr"/>
@@ -3073,7 +3018,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F06, Section 6</t>
+          <t>Related Requirement: M07-F06, Business Rules 6.6</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3030,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3095,41 +3040,39 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Material Attachment</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Dinh kem tai lieu voi dong hoan toan trong (bo qua dong)</t>
+          <t>Attach Material with Completely Empty Row (Ignore Blank Rows)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Verify whether system tu dong bo qua va khong bao error khi co dong tai lieu trong (ca Label va URL deu rong).</t>
+          <t>Verify system ignores completely blank material rows without raising error.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang edit hoac create moi Session/Exam.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Label=""; URL=""</t>
+          <t>Row1={Label: "Slides", Url: "https://drive.google.com/..."}; Row2={Label: "", Url: ""}</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>1. Add mot dong dinh kem tai lieu moi.
-2. De trong ca hai truong Nhan (Label) va URL.
-3. Nhan "Save" (Save).</t>
+          <t>1. Fill Row 1 with valid label and URL;
+2. Leave Row 2 completely empty;
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>System archive successfully cac thong tin khac.
-Dong trong tu dong bi bo qua (skipped) ma not displayed bat ky notification error nao.</t>
+          <t>System saves Row 1 successfully and ignores blank Row 2 without error.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -3145,7 +3088,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F06, Rule 6 (Empty Attachment Rows), Error Handling (Section 9)</t>
+          <t>Related Requirement: M07-F06, Business Rules 6.6</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3100,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3167,41 +3110,40 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Material Attachment</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Dinh kem failed do co Nhan (Label) nhung blank URL</t>
+          <t>Attach Material Fails Due to Label Provided with Empty URL</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Verify system ngan chan save va bao error khi enter nhan tai lieu nhung khong co link.</t>
+          <t>Verify system displays error when Label is filled but URL is empty.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang edit hoac create moi Session/Exam.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Label="Sach tham khao"; URL=""</t>
+          <t>Label="Lecture Slides"; Url=""</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>1. Enter Nhan (Label) la "Sach tham khao".
-2. De trong truong URL.
-3. Nhan "Save" (Save).</t>
+          <t>1. Enter Label as "Lecture Slides";
+2. Leave URL field empty;
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>System bao error requires enter URL cho tai lieu (e.g.: "URL is required when Label is provided.").
-Tai lieu khong duoc save.</t>
+          <t>System blocks action.
+Validation error appears: "URL is required when Label is specified."</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr"/>
@@ -3217,7 +3159,7 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
+          <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3171,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3239,41 +3181,40 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Material Attachment</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Dinh kem failed do co URL nhung blank Nhan (Label)</t>
+          <t>Attach Material Fails Due to URL Provided with Empty Label</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Verify system ngan chan save va bao error khi enter link tai lieu nhung blank nhan.</t>
+          <t>Verify system displays error when URL is filled but Label is empty.</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang edit hoac create moi Session/Exam.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Label=""; URL="https://drive.google.com/file/d/1A2B3/view"</t>
+          <t>Label=""; Url="https://drive.google.com/file/d/123/view"</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>1. De trong truong Nhan (Label).
-2. Enter URL la "https://drive.google.com/file/d/1A2B3/view".
-3. Nhan "Save" (Save).</t>
+          <t>1. Leave Label field empty;
+2. Enter valid Google Drive URL;
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>System bao error requires enter Nhan cho tai lieu (e.g.: "Label is required when URL is provided.").
-Tai lieu khong duoc save.</t>
+          <t>System blocks action.
+Validation error appears: "Label is required when URL is specified."</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -3289,7 +3230,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
+          <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3242,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3311,41 +3252,40 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Material Attachment</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Dinh kem failed do link not Google Drive</t>
+          <t>Attach Material Fails Due to Non-Google Drive Link Domain</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Verify system ngan chan save va bao error format khi enter link tu dich vu archive khac.</t>
+          <t>Verify system restricts material links to Google Drive domain.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang edit hoac create moi Session/Exam.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>Label="Tai lieu"; URL="https://dropbox.com/s/abcdef"</t>
+          <t>Label="External Site"; Url="https://example.com/file.pdf"</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>1. Enter Nhan "Tai lieu".
-2. Enter URL la "https://dropbox.com/s/abcdef".
-3. Nhan "Save" (Save).</t>
+          <t>1. Enter Label as "External Site";
+2. Enter non-Google Drive URL "https://example.com/file.pdf";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>System display error kiem tra format URL (e.g.: "Must start with https://drive.google.com/").
-Tai lieu khong duoc save.</t>
+          <t>System blocks action.
+Validation error appears: "Material link must be a valid Google Drive URL."</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr"/>
@@ -3361,11 +3301,11 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="150" customHeight="1">
+          <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TC-M07-029</t>
@@ -3373,7 +3313,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3383,41 +3323,39 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Xuat danh sach Session ra file CSV (Export CSV)</t>
+          <t>Export Session List to CSV File (Export CSV)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for tai file CSV chua thong tin cac session cua course hien tai.</t>
+          <t>Verify functionality for exporting course session list to a downloadable CSV file.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Dang o interface danh sach Session cua course "Java Programming" chua cac session va tai lieu.</t>
+Course contains sessions.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CourseName="Web Development"</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>1. Nhap nut "Xuat CSV" (Export CSV).</t>
+          <t>1. Open Course "Web Development";
+2. Click Export CSV button.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>System tai ve mot file CSV successfully.
-File CSV co cac cot: Session ID, Session Name, Lesson Number, Description.
-Thong tin cac session khop voi danh sach display tren system.
-Tai lieu dinh kem (Google Drive link) KHONG duoc xuat hien trong file.</t>
+          <t>CSV file downloads successfully containing Session ID, Session Name, and Material details.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -3433,11 +3371,11 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F07, Rule 7 (Export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="135" customHeight="1">
+          <t>Related Requirement: M07-F07, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>TC-M07-030</t>
@@ -3445,7 +3383,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -3455,43 +3393,39 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Enter CSV - Cap nhat thong tin Session da ton tai</t>
+          <t>Import CSV - Update Information of Existing Session</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Verify system cap nhat chinh xac ten, so bai va mo ta cua session khi Session ID trong file CSV trung khop voi session co san.</t>
+          <t>Verify importing CSV with matching Session ID updates existing session details.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Bai hoc voi ID "S001" da ton tai duoi course "Java Programming" co ten cu la "OOP Intro".</t>
+Session ID "SES-001" exists in system.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>File CSV chua dong: Session ID="S001"; Session Name="OOP Basics"; Lesson Number="1"; Description="Gioi thieu huong doi tuong"</t>
+          <t>CsvFile="SessionID=SES-001, SessionName=Updated HTML Basics"</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>1. Select course "Java Programming".
-2. Nhap select "Enter CSV" (Import CSV).
-3. Upload file CSV chua du lieu cap nhat cho ID "S001".
-4. Nhap "Xac nhan".</t>
+          <t>1. Upload CSV containing updated name for SES-001;
+2. Click Import CSV button.</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>System display notification enter du lieu successfully.
-Bai hoc co ID "S001" duoc cap nhat successfully voi ten "OOP Basics", so bai "1", mo ta "Gioi thieu huong doi tuong".
-Cac tai lieu dinh kem truoc do cua session nay van duoc giu nguyen.</t>
+          <t>Session SES-001 is updated with new name "Updated HTML Basics".</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr"/>
@@ -3507,11 +3441,11 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F07, Rule 7.1 (Existing Session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="120" customHeight="1">
+          <t>Related Requirement: M07-F07, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TC-M07-031</t>
@@ -3519,7 +3453,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3529,43 +3463,38 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Enter CSV - Create session moi khi blank Session ID</t>
+          <t>Import CSV - Create New Session when Session ID Is Blank</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Verify system tu dong create moi mot session neu cot Session ID trong dong CSV bi bo trong.</t>
+          <t>Verify importing CSV row with empty Session ID creates a brand new session.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang select course "Java Programming".</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>File CSV chua dong: Session ID=""; Session Name="OOP Polymorphism"; Lesson Number="3"; Description="Tinh da hinh"</t>
+          <t>CsvFile="SessionID=, SessionName=New CSS Grid Session"</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>1. Select course "Java Programming".
-2. Nhap select "Enter CSV" (Import CSV).
-3. Upload file CSV co cot ID blank.
-4. Nhap "Xac nhan".</t>
+          <t>1. Upload CSV containing blank Session ID row;
+2. Click Import CSV button.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>System display notification enter du lieu successfully.
-Mot session moi duoc create ra duoi course "Java Programming" voi ten "OOP Polymorphism", so session "3" va mo ta "Tinh da hinh".
-System tu dong cap phat mot ID moi cho session nay.</t>
+          <t>New session "New CSS Grid Session" is created with auto-generated Session ID.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -3581,11 +3510,11 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F07, Rule 7.2 (New Session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="105" customHeight="1">
+          <t>Related Requirement: M07-F07, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>TC-M07-032</t>
@@ -3593,7 +3522,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -3603,42 +3532,39 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Enter CSV - Create session moi khi Session ID khong ton tai tren system</t>
+          <t>Import CSV - Create New Session when Session ID Does Not Exist in System</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Verify system tu dong create moi session neu Session ID trong CSV khong trung khop voi bat ky session hien co nao.</t>
+          <t>Verify importing CSV row with non-existent Session ID creates a new session.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" khong co session nao mang ID "S999".</t>
+Session ID "SES-999" does not exist.</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>File CSV chua dong: Session ID="S999"; Session Name="Exception Handling"; Lesson Number="4"; Description="Xu ly ngoai le"</t>
+          <t>CsvFile="SessionID=SES-999, SessionName=Flexbox Guide"</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>1. Select course "Java Programming".
-2. Nhap select "Enter CSV" (Import CSV).
-3. Upload file CSV chua dong co ID la "S999".
-4. Nhap "Xac nhan".</t>
+          <t>1. Upload CSV containing non-existent Session ID;
+2. Click Import CSV button.</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>System display notification enter du lieu successfully.
-Mot session moi duoc create ra voi ID moi duoc create hoac cap nhat theo system, ten "Exception Handling" duoc gan duoi course.</t>
+          <t>New session "Flexbox Guide" is created in system.</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr"/>
@@ -3647,18 +3573,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F07, Rule 7.2 (New Session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="105" customHeight="1">
+          <t>Related Requirement: M07-F07, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TC-M07-033</t>
@@ -3666,7 +3592,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3676,42 +3602,39 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Enter CSV - Cac session hien tai khong co trong CSV se giu nguyen</t>
+          <t>Import CSV - Existing Sessions Omitted from CSV Are Retained</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Verify whether system co bao toan cac session san co cua course neu chung khong duoc liet ke trong file CSV tai len.</t>
+          <t>Verify importing CSV does not delete existing sessions that are absent from the CSV file.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" dang co 2 session san co: "S001" va "S002".</t>
+Sessions SES-001 and SES-002 exist.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>File CSV chi chua thong tin cap nhat cho session "S001". Bai hoc "S002" hoan toan khong co trong file.</t>
+          <t>CsvFile="SessionID=SES-001, SessionName=HTML Basics"</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>1. Nhap select "Enter CSV" (Import CSV).
-2. Upload file CSV chi co thong tin cho session "S001".
-3. Nhap "Xac nhan".</t>
+          <t>1. Upload CSV containing only SES-001;
+2. Perform CSV import.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>System notification enter successfully.
-Bai hoc "S001" duoc cap nhat.
-Bai hoc "S002" van ton tai nguyen ven duoi course "Java Programming" ma khong bi delete di.</t>
+          <t>SES-001 is processed, and omitted session SES-002 remains unchanged in system without being deleted.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -3727,11 +3650,11 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F07, Rule 7.3 (Missing Sessions)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="120" customHeight="1">
+          <t>Related Requirement: M07-F07, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>TC-M07-034</t>
@@ -3739,7 +3662,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -3749,43 +3672,38 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Enter CSV - Bo qua cot Materials trong file CSV tai len</t>
+          <t>Import CSV - Skip Materials Column in Uploaded CSV File</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Verify whether system co bo qua cot Materials va khong ghi de hoac gay error neu file CSV chua cot nay.</t>
+          <t>Verify system ignores Materials column when importing session CSV file.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Bai hoc "S001" dang co san mot tai lieu dinh kem la "Slides".</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>File CSV chua cac cot: Session ID, Session Name, Lesson Number, Description, Materials. Dong du lieu: S001, OOP Basics, 1, Gioi thieu huong doi tuong, https://drive.google.com/some-link-to-ignore</t>
+          <t>CsvFile="SessionID=SES-001, SessionName=HTML, Materials=http://..."</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>1. Select course.
-2. Nhap select "Enter CSV" (Import CSV).
-3. Upload file CSV co chua cot Materials voi gia tri link bat ky.
-4. Nhap "Xac nhan".</t>
+          <t>1. Upload CSV containing Materials column;
+2. Click Import CSV button.</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>System display notification enter successfully.
-Thong tin Session duoc cap nhat.
-Tai lieu dinh kem "Slides" ban dau cua Session "S001" van duoc giu nguyen. Link trong cot Materials cua file CSV hoan toan bi bo qua.</t>
+          <t>Sessions are updated/created, and Materials column is safely ignored per business rule.</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr"/>
@@ -3794,18 +3712,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F07, Rule 7.4 (Materials Column)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="90" customHeight="1">
+          <t>Related Requirement: M07-F07, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>TC-M07-035</t>
@@ -3813,7 +3731,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3823,41 +3741,39 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Enter CSV failed do select sai format tep (not CSV)</t>
+          <t>Import CSV Fails Due to Incorrect File Format (Non-CSV File)</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Verify system denies tai len va notification error khi user select tep not duoi .csv.</t>
+          <t>Verify system rejects non-CSV file formats during import.</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang o interface Enter CSV cua course.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Tep tin: document.docx hoac image.png</t>
+          <t>FileName="materials.pdf"</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>1. Nhap select nut "Enter CSV".
-2. Select tai len tep tin "document.docx".
-3. Nhap nut "Xac nhan" hoac system chan ngay khi select tep.</t>
+          <t>1. Select non-CSV file "materials.pdf" in import dialog;
+2. Click Import CSV button.</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>System denies tep tin va display notification error format tep khong hop le (e.g.: "Invalid file format. Please upload a CSV file.").
-Khong co hanh dong enter du lieu nao duoc thuc hien.</t>
+          <t>System blocks import.
+Error message appears: "Invalid file format. Please upload a CSV file."</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
@@ -3873,11 +3789,11 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Related to Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="75" customHeight="1">
+          <t>Related Requirement: M07-F07, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>TC-M07-036</t>
@@ -3885,7 +3801,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -3895,41 +3811,38 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>CSV Export / Import</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Enter CSV failed for dong thieu thong tin Ten session</t>
+          <t>Import CSV Fails for Rows Missing Session Name</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Verify system ngan chan viec create session moi qua CSV neu dong do thieu Ten session.</t>
+          <t>Verify system skips or flags error for CSV rows missing mandatory Session Name.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang select course "Java Programming".</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>File CSV chua dong: Session ID=""; Session Name=""; Lesson Number="5"; Description="Bai hoc thieu ten"</t>
+          <t>CsvFile="SessionID=SES-003, SessionName="</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>1. Nhap select "Enter CSV" (Import CSV).
-2. Upload file CSV chua dong du lieu error noi tren.
-3. Nhan "Xac nhan".</t>
+          <t>1. Upload CSV containing row with empty Session Name;
+2. Click Import CSV button.</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>System bao error kiem tra du lieu o dong tuong ung (e.g.: "Row X: Session Name is required.").
-Dong error do khong duoc import vao system.</t>
+          <t>System flags error for row or skips invalid row with warning message: "Session Name is required."</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr"/>
@@ -3945,11 +3858,11 @@
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="75" customHeight="1">
+          <t>Related Requirement: M07-F07, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>TC-M07-037</t>
@@ -3957,49 +3870,48 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>M07-SEC</t>
+          <t>M07-F08</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Access Control &amp; Security</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Quyen access - Staff access va thao tac day du tinh nang</t>
+          <t>Access Control - Staff Role Has Full Management Access</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Verify account co email domain @passerellesnumeriques.org duoc cap toan quyen quan tri module.</t>
+          <t>Verify Staff users have full CRUD permissions for categories, courses, sessions, exams, and materials.</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung da log in bang Google OAuth voi account staff@passerellesnumeriques.org.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Role="Staff"</t>
+          <t>StaffEmail="staff@passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cap vao trang Quan ly Tai lieu hoc tap.
-2. Thuc hien cac thao tac: Rename Category, Add course, Delete session, Enter/Xuat CSV.</t>
+          <t>1. Access Training Materials module;
+2. Verify presence of Create, Edit, Archive, and Delete buttons.</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung access successfully.
-Tat ca cac nut chuc nang hoat dong binh thuong ma khong bi chan quyen.</t>
+          <t>Staff user can perform all management operations cleanly.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr"/>
@@ -4015,11 +3927,11 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Related to Docs/docs.md Section 4 (User Roles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="135" customHeight="1">
+          <t>Related Requirement: M07-F08, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>TC-M07-038</t>
@@ -4027,50 +3939,49 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>M07-SEC</t>
+          <t>M07-F08</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Access Control &amp; Security</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Quyen access - Hoc vien (Student) bi han che cac quyen quan ly</t>
+          <t>Access Control - Student Role Has Read-Only Access</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Verify account student co email domain @student.passerellesnumeriques.org cannot thuc hien cac thao tac quan ly (Add/Sua/Delete/Archive/Import/Export) tren module.</t>
+          <t>Verify Student users can view training materials but cannot create, edit, or delete items.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung da log in bang Google OAuth voi account student@student.passerellesnumeriques.org.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>Role="Student"</t>
+          <t>StudentEmail="student@student.passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>1. Co gang access truc tiep vao duong dan Quan ly Tai lieu hoc tap (neu co), hoac kiem tra interface Student Portal.
-2. Observe su ton tai cua cac nut chuc nang doi ten, add course, delete session, import CSV.</t>
+          <t>1. Access Training Materials module as Student;
+2. Check for management buttons.</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>Hoc vien khong co quyen access trang quan tri Staff.
-Khong display cac nut chuc nang quan ly tai lieu hoc tap tren man hinh danh cho student.
-System display notification error hoac denies access (Access Denied) neu co access qua URL truc tiep.</t>
+          <t>Create, Edit, Archive, Delete, and CSV Import buttons are completely hidden.
+Student can view and open material links in Read-Only mode.</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr"/>
@@ -4086,11 +3997,11 @@
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>Related to Docs/docs.md Section 4 (User Roles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="75" customHeight="1">
+          <t>Related Requirement: M07-F08, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>TC-M07-039</t>
@@ -4098,48 +4009,47 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>M07-SEC</t>
+          <t>M07-F08</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Access Control &amp; Security</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Quyen access - Domain la bi denies access system</t>
+          <t>Access Control - External Domain Accounts Are Denied Access</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Verify system denies access ngay lap tuc for email khong thuoc 2 domain duoc cau hinh.</t>
+          <t>Verify accounts outside organizational domains are denied access.</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung da log in bang Google OAuth voi account user@gmail.com.</t>
+          <t>User attempts access with external personal account.</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Role="Unknown"</t>
+          <t>UserEmail="user@gmail.com"</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>1. Co gang access system Academic Portal.</t>
+          <t>1. Attempt to access Training Materials URL with external email.</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>System display trang denies access (Access Denied).
-Khong display bat ky thong tin nao ve cac category tai lieu hoac course.</t>
+          <t>Access denied page or login redirect is displayed.</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
@@ -4155,11 +4065,11 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Related to Docs/docs.md Section 4 &amp; Section 6 (Authentication Flow)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="120" customHeight="1">
+          <t>Related Requirement: M07-F08, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t>TC-M07-040</t>
@@ -4167,7 +4077,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -4177,41 +4087,39 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Course Archiving / Restoring</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Verify an tu dong tat ca Session/Exam con khi Archive course</t>
+          <t>Verify Auto-hiding All Child Sessions/Exams When Course Is Archived</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Verify rang khi archive mot course, tat ca cac session (session) va exam (exam) thuoc course do tu dong bien mat khoi interface chung cua user, nhung du lieu van ton tai trong co so du lieu.</t>
+          <t>Verify archiving a course automatically hides all nested sessions and exams.</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" dang hoat dong va co session "Session 01" cung exam "Midterm Exam" dang display.</t>
+Course "Web Development" contains 3 sessions and 1 exam.</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"</t>
+          <t>CourseName="Web Development"</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>1. Thuc hien archive course "Java Programming".
-2. Truy cap hoac kiem tra danh sach session va exam tren interface display tai lieu chung.</t>
+          <t>1. Archive course "Web Development";
+2. View course list as Student.</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Khoa hoc chuyen sang status da archive.
-Bai hoc "Session 01" va exam "Midterm Exam" khong con xuat hien tren interface display tai lieu hoc tap chung.
-Verify co so du lieu de dam bao cac ban ghi nay van ton tai.</t>
+          <t>Course and all its child sessions and exams are hidden from active view.</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr"/>
@@ -4227,11 +4135,11 @@
       </c>
       <c r="N41" s="9" t="inlineStr">
         <is>
-          <t>Related to M07-F03, Rule 5.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="90" customHeight="1">
+          <t>Related Requirement: M07-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>TC-M07-041</t>
@@ -4239,7 +4147,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Module 07 – Training Materials</t>
+          <t>Module 07 - Training Materials</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -4249,40 +4157,39 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Course Archiving / Restoring</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Verify khoi phuc display tat ca Session/Exam con khi Khoi phuc course</t>
+          <t>Verify Restoring All Child Sessions/Exams When Course Is Restored</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Verify rang khi khoi phuc mot course da archive, tat ca cac session (session) va exam (exam) thuoc course do tu dong display tro lai tren interface.</t>
+          <t>Verify restoring an archived course restores visibility of all nested sessions and exams.</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Khoa hoc "Java Programming" dang o status Archive (Archived), cac session va exam con dang bi an display.</t>
+Course "Web Development" is Archived.</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"</t>
+          <t>CourseName="Web Development"</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>1. Thuc hien khoi phuc course "Java Programming".
-2. Truy cap vao interface display session va exam cua course nay.</t>
+          <t>1. Restore course "Web Development";
+2. View active course list.</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Khoa hoc chuyen sang status Hoat dong (Active).
-Bai hoc "Session 01" va exam "Midterm Exam" tu dong xuat hien tro lai tren interface display va can xem/edit binh thuong.</t>
+          <t>Course and all child sessions and exams reappear in active view.</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
@@ -4298,7 +4205,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Related to M07-F03, Rule 5.3</t>
+          <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module07_test_cases.xlsx
+++ b/Tests/excel/module07_test_cases.xlsx
@@ -2,31 +2,155 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Module07" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module07'!$A$1:$N$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module07'!$A$1:$N$41</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFA50E0E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFB06000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF137333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E293B"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFA50E0E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFB06000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF137333"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00137333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A50E0E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -48,37 +172,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0064748B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00A50E0E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
       <color rgb="00B06000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -130,7 +224,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -139,8 +233,74 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE8E6"/>
+        <bgColor rgb="FFFCE8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF7E0"/>
+        <bgColor rgb="FFFEF7E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
+        <bgColor rgb="FFE2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4EA"/>
+        <bgColor rgb="FFE6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE8E6"/>
+        <bgColor rgb="00FCE8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -151,38 +311,64 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE8E6"/>
-        <bgColor rgb="00FCE8E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEF7E0"/>
         <bgColor rgb="00FEF7E0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
-        <bgColor rgb="00E2E8F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1E293B"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF1E293B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -220,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -321,9 +507,93 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -896,326 +1166,326 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>Module 07 - Feature &amp; Priority Summary Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Summary of test cases per feature, calculated via Excel formulas</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>Total Features</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>High Priority Features</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>Medium Priority Features</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>Low Priority Features</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="14">
+      <c r="A5" s="44">
         <f>COUNTA(A9:A15)</f>
         <v/>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="45">
         <f>F16</f>
         <v/>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="46">
         <f>COUNTIF(C9:C15, "&gt;0")</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="47">
         <f>COUNTIFS(C9:C15, 0, D9:D15, "&gt;0")</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="48">
         <f>COUNTIFS(C9:C15, 0, D9:D15, 0, E9:E15, "&gt;0")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Feature Categorization &amp; Priority Breakdown</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Feature ID</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>Feature Name</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>High Priority</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>Medium Priority</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="50" t="inlineStr">
         <is>
           <t>Low Priority</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>Total TCs</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>M07-F02</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>Category Management</t>
         </is>
       </c>
-      <c r="C9" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$M$2:$M$42, "High")</f>
+      <c r="C9" s="54">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A9, 'Module07'!$M$2:$M$41, "High")</f>
         <v/>
       </c>
-      <c r="D9" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="D9" s="55">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A9, 'Module07'!$M$2:$M$41, "Medium")</f>
         <v/>
       </c>
-      <c r="E9" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="E9" s="56">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A9, 'Module07'!$M$2:$M$41, "Low")</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="57">
         <f>SUM(C9:E9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>M07-F03</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Course Management</t>
         </is>
       </c>
-      <c r="C10" s="30">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$M$2:$M$42, "High")</f>
+      <c r="C10" s="60">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A10, 'Module07'!$M$2:$M$41, "High")</f>
         <v/>
       </c>
-      <c r="D10" s="31">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="D10" s="61">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A10, 'Module07'!$M$2:$M$41, "Medium")</f>
         <v/>
       </c>
-      <c r="E10" s="32">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="E10" s="62">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A10, 'Module07'!$M$2:$M$41, "Low")</f>
         <v/>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="63">
         <f>SUM(C10:E10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>M07-F04</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>Session Management</t>
         </is>
       </c>
-      <c r="C11" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$M$2:$M$42, "High")</f>
+      <c r="C11" s="54">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A11, 'Module07'!$M$2:$M$41, "High")</f>
         <v/>
       </c>
-      <c r="D11" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="D11" s="55">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A11, 'Module07'!$M$2:$M$41, "Medium")</f>
         <v/>
       </c>
-      <c r="E11" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="E11" s="56">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A11, 'Module07'!$M$2:$M$41, "Low")</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="57">
         <f>SUM(C11:E11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>M07-F05</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>Exam Management</t>
         </is>
       </c>
-      <c r="C12" s="30">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$M$2:$M$42, "High")</f>
+      <c r="C12" s="60">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A12, 'Module07'!$M$2:$M$41, "High")</f>
         <v/>
       </c>
-      <c r="D12" s="31">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="D12" s="61">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A12, 'Module07'!$M$2:$M$41, "Medium")</f>
         <v/>
       </c>
-      <c r="E12" s="32">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="E12" s="62">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A12, 'Module07'!$M$2:$M$41, "Low")</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="63">
         <f>SUM(C12:E12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>M07-F06</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>Material Link Attachment</t>
         </is>
       </c>
-      <c r="C13" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$M$2:$M$42, "High")</f>
+      <c r="C13" s="54">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A13, 'Module07'!$M$2:$M$41, "High")</f>
         <v/>
       </c>
-      <c r="D13" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="D13" s="55">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A13, 'Module07'!$M$2:$M$41, "Medium")</f>
         <v/>
       </c>
-      <c r="E13" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="E13" s="56">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A13, 'Module07'!$M$2:$M$41, "Low")</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="57">
         <f>SUM(C13:E13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>M07-F07</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>CSV Export &amp; Import</t>
         </is>
       </c>
-      <c r="C14" s="30">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$M$2:$M$42, "High")</f>
+      <c r="C14" s="60">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A14, 'Module07'!$M$2:$M$41, "High")</f>
         <v/>
       </c>
-      <c r="D14" s="31">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="D14" s="61">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A14, 'Module07'!$M$2:$M$41, "Medium")</f>
         <v/>
       </c>
-      <c r="E14" s="32">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="E14" s="62">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A14, 'Module07'!$M$2:$M$41, "Low")</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="63">
         <f>SUM(C14:E14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>M07-F08</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="53" t="inlineStr">
         <is>
           <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
-      <c r="C15" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$M$2:$M$42, "High")</f>
+      <c r="C15" s="54">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A15, 'Module07'!$M$2:$M$41, "High")</f>
         <v/>
       </c>
-      <c r="D15" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$M$2:$M$42, "Medium")</f>
+      <c r="D15" s="55">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A15, 'Module07'!$M$2:$M$41, "Medium")</f>
         <v/>
       </c>
-      <c r="E15" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$M$2:$M$42, "Low")</f>
+      <c r="E15" s="56">
+        <f>COUNTIFS('Module07'!$C$2:$C$41, A15, 'Module07'!$M$2:$M$41, "Low")</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="57">
         <f>SUM(C15:E15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="65">
         <f>COUNTA(A9:A15)&amp;" Features"</f>
         <v/>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="64">
         <f>SUM(C9:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="64">
         <f>SUM(D9:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="64">
         <f>SUM(E9:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="64">
         <f>SUM(F9:F15)</f>
         <v/>
       </c>
@@ -1232,26 +1502,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="9" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1379,10 +1647,14 @@
 New category name "Foundations" is updated and displayed on UI.</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Category renamed successfully. New category name "Foundations" was updated and displayed on UI.</t>
+        </is>
+      </c>
+      <c r="L2" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -1450,10 +1722,14 @@
 Validation error message appears: "Category Name cannot be empty."</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error message: "Category Name cannot be empty."</t>
+        </is>
+      </c>
+      <c r="L3" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -1520,10 +1796,14 @@
           <t>Archive and Delete buttons are not present in Category context menu.</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Archive and Delete options were not present in Category context menu as expected.</t>
+        </is>
+      </c>
+      <c r="L4" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
@@ -1589,10 +1869,14 @@
           <t>Default categories "IT", "English", and "Professional Skills" are present in system.</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Default categories "IT", "English", and "Professional Skills" were present in system.</t>
+        </is>
+      </c>
+      <c r="L5" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -1662,10 +1946,14 @@
 New course "Web Development" appears under category "IT".</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Course created successfully. New course "Web Development" appeared under category "IT".</t>
+        </is>
+      </c>
+      <c r="L6" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
@@ -1732,10 +2020,14 @@
 Validation error appears: "Course Name is required."</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Course Name is required."</t>
+        </is>
+      </c>
+      <c r="L7" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -1804,10 +2096,14 @@
           <t>Course name updated successfully to "Frontend Development".</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Course name updated successfully to "Frontend Development".</t>
+        </is>
+      </c>
+      <c r="L8" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -1875,10 +2171,14 @@
 Course is hidden from Active list and moved to Archived tab.</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Course status changed to Archived. Course was hidden from Active list and moved to Archived tab.</t>
+        </is>
+      </c>
+      <c r="L9" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -1947,10 +2247,14 @@
 Course reappears in active course list.</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Course status changed back to Active. Course reappeared in active course list.</t>
+        </is>
+      </c>
+      <c r="L10" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -2017,10 +2321,14 @@
           <t>Permanent Delete button is not present for courses (only Archive is supported).</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Permanent Delete button was not present for courses; only Archive option was supported.</t>
+        </is>
+      </c>
+      <c r="L11" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
@@ -2090,10 +2398,14 @@
 "Session 1: HTML Basics" appears inside course.</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Session created successfully. "Session 1: HTML Basics" appeared inside course.</t>
+        </is>
+      </c>
+      <c r="L12" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -2160,10 +2472,14 @@
 Validation error appears: "Session Name is required."</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Session Name is required."</t>
+        </is>
+      </c>
+      <c r="L13" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -2231,10 +2547,14 @@
           <t>Session details updated successfully.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Session details were updated successfully as expected.</t>
+        </is>
+      </c>
+      <c r="L14" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -2301,10 +2621,14 @@
           <t>Session and all attached materials are permanently deleted from system.</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Session and all attached materials were permanently deleted from system.</t>
+        </is>
+      </c>
+      <c r="L15" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -2372,10 +2696,14 @@
 Session remains intact in course.</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Confirmation dialog closed and session remained intact in course.</t>
+        </is>
+      </c>
+      <c r="L16" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
@@ -2440,10 +2768,14 @@
           <t>Archive button is not available for sessions (only Delete is supported).</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>Archive button was not available for sessions; only Delete was supported.</t>
+        </is>
+      </c>
+      <c r="L17" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
@@ -2513,10 +2845,14 @@
 "Midterm Exam" displays in exam section of course.</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Exam created successfully. "Midterm Exam" displayed in exam section of course.</t>
+        </is>
+      </c>
+      <c r="L18" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -2583,10 +2919,14 @@
 Validation error appears: "Exam Name is required."</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Exam Name is required."</t>
+        </is>
+      </c>
+      <c r="L19" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -2654,10 +2994,14 @@
           <t>Exam details updated successfully.</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Exam details were updated successfully as expected.</t>
+        </is>
+      </c>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -2724,10 +3068,14 @@
           <t>Exam and all attached exam materials are permanently deleted from system.</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Exam and all attached exam materials were permanently deleted from system.</t>
+        </is>
+      </c>
+      <c r="L21" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -2795,10 +3143,14 @@
 Exam remains intact in course.</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Confirmation dialog closed and exam remained intact in course.</t>
+        </is>
+      </c>
+      <c r="L22" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
@@ -2863,10 +3215,14 @@
           <t>Archive button is not available for exams (only Delete is supported).</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Archive button was not available for exams; only Delete was supported.</t>
+        </is>
+      </c>
+      <c r="L23" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
@@ -2935,10 +3291,14 @@
           <t>Material link is attached successfully and clickable on UI.</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Material link was attached successfully and clickable on UI as expected.</t>
+        </is>
+      </c>
+      <c r="L24" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -3005,10 +3365,14 @@
           <t>All material links are attached and displayed under session/exam.</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>All material links were attached and displayed under session/exam as expected.</t>
+        </is>
+      </c>
+      <c r="L25" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -3075,10 +3439,14 @@
           <t>System saves Row 1 successfully and ignores blank Row 2 without error.</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>System saved Row 1 successfully and ignored blank Row 2 without error.</t>
+        </is>
+      </c>
+      <c r="L26" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
@@ -3146,10 +3514,14 @@
 Validation error appears: "URL is required when Label is specified."</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>The system saves the document link successfully even though the URL field is empty. No validation error message is displayed, and the attached document link does not appear in the document list after saving.</t>
+        </is>
+      </c>
+      <c r="L27" s="40" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -3162,8 +3534,9 @@
           <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="75" customHeight="1">
+      <c r="O27" s="36" t="n"/>
+    </row>
+    <row r="28" ht="90.75" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>TC-M07-027</t>
@@ -3217,10 +3590,14 @@
 Validation error appears: "Label is required when URL is specified."</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>The system saves the document link successfully even though the Label field is empty. No validation error message is displayed, and the attached document link does not appear in the document list after saving.</t>
+        </is>
+      </c>
+      <c r="L28" s="40" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -3233,6 +3610,7 @@
           <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
         </is>
       </c>
+      <c r="O28" s="37" t="n"/>
     </row>
     <row r="29" ht="75" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -3288,10 +3666,14 @@
 Validation error appears: "Material link must be a valid Google Drive URL."</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Material link must be a valid Google Drive URL."</t>
+        </is>
+      </c>
+      <c r="L29" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -3358,10 +3740,14 @@
           <t>CSV file downloads successfully containing Session ID, Session Name, and Material details.</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>CSV file downloaded successfully containing Session ID, Session Name, and Material details.</t>
+        </is>
+      </c>
+      <c r="L30" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -3374,6 +3760,7 @@
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
       </c>
+      <c r="O30" s="37" t="n"/>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -3428,10 +3815,14 @@
           <t>Session SES-001 is updated with new name "Updated HTML Basics".</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Session SES-001 was updated with new name "Updated HTML Basics".</t>
+        </is>
+      </c>
+      <c r="L31" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
@@ -3444,6 +3835,7 @@
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
       </c>
+      <c r="O31" s="36" t="n"/>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3497,10 +3889,14 @@
           <t>New session "New CSS Grid Session" is created with auto-generated Session ID.</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>New session "New CSS Grid Session" was created with auto-generated Session ID.</t>
+        </is>
+      </c>
+      <c r="L32" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -3513,6 +3909,7 @@
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
       </c>
+      <c r="O32" s="37" t="n"/>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -3553,7 +3950,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>CsvFile="SessionID=SES-999, SessionName=Flexbox Guide"</t>
+          <t>CsvFile="SessionID=3, SessionName=Flexbox Guide"</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -3567,10 +3964,14 @@
           <t>New session "Flexbox Guide" is created in system.</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>The system does not create a new session. Instead, the import is skipped and the message "Row 2: session ID 3 not found" is displayed. No changes are made.</t>
+        </is>
+      </c>
+      <c r="L33" s="40" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
@@ -3583,6 +3984,7 @@
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
       </c>
+      <c r="O33" s="38" t="n"/>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -3637,10 +4039,14 @@
           <t>SES-001 is processed, and omitted session SES-002 remains unchanged in system without being deleted.</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>SES-001 was processed, and omitted session SES-002 remained unchanged in system without being deleted.</t>
+        </is>
+      </c>
+      <c r="L34" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -3653,6 +4059,7 @@
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
       </c>
+      <c r="O34" s="38" t="n"/>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -3706,10 +4113,14 @@
           <t>Sessions are updated/created, and Materials column is safely ignored per business rule.</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Sessions were updated/created, and Materials column was safely ignored per business rule.</t>
+        </is>
+      </c>
+      <c r="L35" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
@@ -3722,6 +4133,7 @@
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
       </c>
+      <c r="O35" s="38" t="n"/>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3776,10 +4188,14 @@
 Error message appears: "Invalid file format. Please upload a CSV file."</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>System blocked import and displayed error message: "Invalid file format. Please upload a CSV file."</t>
+        </is>
+      </c>
+      <c r="L36" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -3792,6 +4208,7 @@
           <t>Related Requirement: M07-F07, Validation Rules (Section 8)</t>
         </is>
       </c>
+      <c r="O36" s="38" t="n"/>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -3845,10 +4262,14 @@
           <t>System flags error for row or skips invalid row with warning message: "Session Name is required."</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>System flagged error for invalid row with warning message: "Session Name is required."</t>
+        </is>
+      </c>
+      <c r="L37" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -3861,6 +4282,7 @@
           <t>Related Requirement: M07-F07, Validation Rules (Section 8)</t>
         </is>
       </c>
+      <c r="O37" s="38" t="n"/>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3914,10 +4336,14 @@
           <t>Staff user can perform all management operations cleanly.</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Staff user was able to perform all management operations cleanly.</t>
+        </is>
+      </c>
+      <c r="L38" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -3930,64 +4356,67 @@
           <t>Related Requirement: M07-F08, User Roles</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="75" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="O38" s="38" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>TC-M07-038</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Module 07 - Training Materials</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>M07-F08</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Access Control - Student Role Has Read-Only Access</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Verify Student users can view training materials but cannot create, edit, or delete items.</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in as Student.</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>StudentEmail="student@student.passerellesnumeriques.org"</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>1. Access Training Materials module as Student;
-2. Check for management buttons.</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Create, Edit, Archive, Delete, and CSV Import buttons are completely hidden.
-Student can view and open material links in Read-Only mode.</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Access Control - External Domain Accounts Are Denied Access</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Verify accounts outside organizational domains are denied access.</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>User attempts access with external personal account.</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>UserEmail="user@gmail.com"</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt to access Training Materials URL with external email.</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Access denied page or login redirect is displayed.</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Access denied page was displayed for external domain accounts as expected.</t>
+        </is>
+      </c>
+      <c r="L39" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -3995,227 +4424,170 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F08, User Roles</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="O39" s="38" t="n"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>TC-M07-039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Module 07 - Training Materials</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>M07-F08</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Role Permissions &amp; Access Control</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Access Control - External Domain Accounts Are Denied Access</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Verify accounts outside organizational domains are denied access.</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>User attempts access with external personal account.</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>UserEmail="user@gmail.com"</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>1. Attempt to access Training Materials URL with external email.</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Access denied page or login redirect is displayed.</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M07-F08, User Roles</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>TC-M07-040</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Module 07 - Training Materials</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>M07-F03</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Course Management</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Verify Auto-hiding All Child Sessions/Exams When Course Is Archived</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>Verify archiving a course automatically hides all nested sessions and exams.</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
 Course "Web Development" contains 3 sessions and 1 exam.</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>CourseName="Web Development"</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>1. Archive course "Web Development";
 2. View course list as Student.</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>Course and all its child sessions and exams are hidden from active view.</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>Course and all child sessions and exams were hidden from active view upon course archiving.</t>
+        </is>
+      </c>
+      <c r="L40" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TC-M07-041</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="O40" s="38" t="n"/>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TC-M07-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Module 07 - Training Materials</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>M07-F03</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Course Management</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Verify Restoring All Child Sessions/Exams When Course Is Restored</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Verify restoring an archived course restores visibility of all nested sessions and exams.</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
 Course "Web Development" is Archived.</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>CourseName="Web Development"</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>1. Restore course "Web Development";
 2. View active course list.</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>Course and all child sessions and exams reappear in active view.</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Course and all child sessions and exams reappeared in active view upon course restoration.</t>
+        </is>
+      </c>
+      <c r="L41" s="39" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
       </c>
+      <c r="O41" s="38" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N42"/>
+  <autoFilter ref="A1:N41"/>
   <dataValidations count="2">
-    <dataValidation sqref="L2:L142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
+    <dataValidation sqref="L2:L141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="M2:M141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tests/excel/module07_test_cases.xlsx
+++ b/Tests/excel/module07_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Module07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module07" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module07'!$A$1:$N$42</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Tests/excel/module07_test_cases.xlsx
+++ b/Tests/excel/module07_test_cases.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module07" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module07'!$A$1:$N$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module07'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1009,15 +1009,15 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$M$2:$M$42, "High")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$N$2:$N$42, "High")</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$M$2:$M$42, "Medium")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$N$2:$N$42, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$M$2:$M$42, "Low")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A9, 'Module07'!$N$2:$N$42, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="27">
@@ -1037,15 +1037,15 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$M$2:$M$42, "High")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$N$2:$N$42, "High")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$M$2:$M$42, "Medium")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$N$2:$N$42, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$M$2:$M$42, "Low")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A10, 'Module07'!$N$2:$N$42, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="33">
@@ -1065,15 +1065,15 @@
         </is>
       </c>
       <c r="C11" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$M$2:$M$42, "High")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$N$2:$N$42, "High")</f>
         <v/>
       </c>
       <c r="D11" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$M$2:$M$42, "Medium")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$N$2:$N$42, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$M$2:$M$42, "Low")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A11, 'Module07'!$N$2:$N$42, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="27">
@@ -1093,15 +1093,15 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$M$2:$M$42, "High")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$N$2:$N$42, "High")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$M$2:$M$42, "Medium")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$N$2:$N$42, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$M$2:$M$42, "Low")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A12, 'Module07'!$N$2:$N$42, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="33">
@@ -1121,15 +1121,15 @@
         </is>
       </c>
       <c r="C13" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$M$2:$M$42, "High")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$N$2:$N$42, "High")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$M$2:$M$42, "Medium")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$N$2:$N$42, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$M$2:$M$42, "Low")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A13, 'Module07'!$N$2:$N$42, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1149,15 +1149,15 @@
         </is>
       </c>
       <c r="C14" s="30">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$M$2:$M$42, "High")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$N$2:$N$42, "High")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$M$2:$M$42, "Medium")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$N$2:$N$42, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$M$2:$M$42, "Low")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A14, 'Module07'!$N$2:$N$42, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="33">
@@ -1177,15 +1177,15 @@
         </is>
       </c>
       <c r="C15" s="24">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$M$2:$M$42, "High")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$N$2:$N$42, "High")</f>
         <v/>
       </c>
       <c r="D15" s="25">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$M$2:$M$42, "Medium")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$N$2:$N$42, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$M$2:$M$42, "Low")</f>
+        <f>COUNTIFS('Module07'!$C$2:$C$42, A15, 'Module07'!$N$2:$N$42, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1232,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1247,8 +1247,9 @@
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1314,10 +1315,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1385,12 +1391,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F02, Rule 6.2</t>
         </is>
@@ -1456,12 +1463,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F02, Validation Rules (Section 8)</t>
         </is>
@@ -1526,12 +1534,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F02, Business Rules 6.2</t>
         </is>
@@ -1595,12 +1604,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F02, Business Rules 6.2</t>
         </is>
@@ -1668,12 +1678,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
@@ -1738,12 +1749,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Validation Rules (Section 8)</t>
         </is>
@@ -1810,12 +1822,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
@@ -1881,12 +1894,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
@@ -1953,12 +1967,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
@@ -2023,12 +2038,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
@@ -2096,12 +2112,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F04, Business Rules 6.4</t>
         </is>
@@ -2166,12 +2183,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F04, Validation Rules (Section 8)</t>
         </is>
@@ -2237,12 +2255,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F04, Business Rules 6.4</t>
         </is>
@@ -2307,12 +2326,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F04, Business Rules 6.4</t>
         </is>
@@ -2378,12 +2398,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F04, UI Standards</t>
         </is>
@@ -2446,12 +2467,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F04, Business Rules 6.4</t>
         </is>
@@ -2519,12 +2541,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F05, Business Rules 6.5</t>
         </is>
@@ -2589,12 +2612,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F05, Validation Rules (Section 8)</t>
         </is>
@@ -2660,12 +2684,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F05, Business Rules 6.5</t>
         </is>
@@ -2730,12 +2755,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F05, Business Rules 6.5</t>
         </is>
@@ -2801,12 +2827,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F05, UI Standards</t>
         </is>
@@ -2869,12 +2896,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F05, Business Rules 6.5</t>
         </is>
@@ -2941,12 +2969,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F06, Business Rules 6.6</t>
         </is>
@@ -3011,12 +3040,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F06, Business Rules 6.6</t>
         </is>
@@ -3081,12 +3111,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F06, Business Rules 6.6</t>
         </is>
@@ -3152,12 +3183,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr">
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
         </is>
@@ -3223,12 +3255,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
         </is>
@@ -3294,12 +3327,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr">
+      <c r="O29" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F06, Validation Rules (Section 8)</t>
         </is>
@@ -3364,12 +3398,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
@@ -3434,12 +3469,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="O31" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
@@ -3503,12 +3539,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
@@ -3573,12 +3610,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
+      <c r="O33" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
@@ -3643,12 +3681,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
@@ -3712,12 +3751,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr">
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Business Rules 6.7</t>
         </is>
@@ -3782,12 +3822,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Validation Rules (Section 8)</t>
         </is>
@@ -3851,12 +3892,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr">
+      <c r="O37" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F07, Validation Rules (Section 8)</t>
         </is>
@@ -3920,12 +3962,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F08, User Roles</t>
         </is>
@@ -3990,12 +4033,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr">
+      <c r="O39" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F08, User Roles</t>
         </is>
@@ -4058,12 +4102,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M40" s="6" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F08, User Roles</t>
         </is>
@@ -4128,12 +4173,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="O41" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
@@ -4198,24 +4244,25 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M07-F03, Business Rules 6.3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N42"/>
+  <autoFilter ref="A1:O42"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="N2:N142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tests/excel/module07_test_cases.xlsx
+++ b/Tests/excel/module07_test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test-case-academic-portal\Tests\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DA6D1D-4EB3-417A-B47D-8ECB85E3082B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C9123D-8CE4-4846-A122-5AECC3E77FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4237,7 +4237,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="147" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>246</v>
       </c>

--- a/Tests/excel/module07_test_cases.xlsx
+++ b/Tests/excel/module07_test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test-case-academic-portal\Tests\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C9123D-8CE4-4846-A122-5AECC3E77FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02FA9A2-B9B7-43FE-B1E0-7FEB5182947D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,28 +34,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2145,70 +2123,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2873,7 +2787,7 @@
       <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="35" t="s">
+      <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="36" t="s">
@@ -4274,9 +4188,7 @@
       <c r="L33" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="M33" s="6" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="M33" s="6"/>
       <c r="N33" s="9" t="s">
         <v>43</v>
       </c>
